--- a/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1975.05</v>
+        <v>28403.01</v>
       </c>
       <c r="C4" t="n">
-        <v>589176</v>
+        <v>5211864</v>
       </c>
       <c r="D4" t="n">
-        <v>462924</v>
+        <v>4095036</v>
       </c>
       <c r="E4" t="n">
-        <v>148500</v>
+        <v>1611000</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>6900</v>
+        <v>83940</v>
       </c>
       <c r="H4" t="n">
-        <v>240</v>
+        <v>7530</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21150</v>
+        <v>177840</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3625.74</v>
+        <v>24284.43</v>
       </c>
       <c r="C5" t="n">
-        <v>670824</v>
+        <v>4122216</v>
       </c>
       <c r="D5" t="n">
-        <v>527076</v>
+        <v>3238884</v>
       </c>
       <c r="E5" t="n">
-        <v>138600</v>
+        <v>1078200</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G5" t="n">
-        <v>8850</v>
+        <v>68460</v>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>5190</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20580</v>
+        <v>151320</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4049.73</v>
+        <v>22312.08</v>
       </c>
       <c r="C6" t="n">
-        <v>507024</v>
+        <v>3628800</v>
       </c>
       <c r="D6" t="n">
-        <v>398376</v>
+        <v>2851200</v>
       </c>
       <c r="E6" t="n">
-        <v>79200</v>
+        <v>765900</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>8190</v>
+        <v>62850</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7560</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>22320</v>
+        <v>149250</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3182.85</v>
+        <v>31681.26</v>
       </c>
       <c r="C7" t="n">
-        <v>286272</v>
+        <v>4630752</v>
       </c>
       <c r="D7" t="n">
-        <v>224928</v>
+        <v>3638448</v>
       </c>
       <c r="E7" t="n">
-        <v>44100</v>
+        <v>944100</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>5460</v>
+        <v>83820</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>12270</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>14760</v>
+        <v>193680</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1673.46</v>
+        <v>30234.24</v>
       </c>
       <c r="C8" t="n">
-        <v>98280</v>
+        <v>2899512</v>
       </c>
       <c r="D8" t="n">
-        <v>77220</v>
+        <v>2278188</v>
       </c>
       <c r="E8" t="n">
-        <v>20700</v>
+        <v>360900</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2370</v>
+        <v>70080</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4230</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5460</v>
+        <v>155160</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>788.58</v>
+        <v>24743.61</v>
       </c>
       <c r="C9" t="n">
-        <v>38304</v>
+        <v>1900584</v>
       </c>
       <c r="D9" t="n">
-        <v>30096</v>
+        <v>1493316</v>
       </c>
       <c r="E9" t="n">
-        <v>11700</v>
+        <v>158400</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1140</v>
+        <v>37080</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1050</v>
+        <v>88620</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>449.37</v>
+        <v>17473.14</v>
       </c>
       <c r="C10" t="n">
-        <v>12096</v>
+        <v>1078056</v>
       </c>
       <c r="D10" t="n">
-        <v>9504</v>
+        <v>847044</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>63900</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>690</v>
+        <v>30690</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10095,13 +10089,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>690</v>
+        <v>46530</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>291.24</v>
+        <v>2873.43</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>206136</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>161964</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>4110</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>13050</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>163.98</v>
+        <v>428.85</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>55944</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>43956</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>129.6</v>
+        <v>183.96</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>13608</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>10692</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>141.12</v>
+        <v>144.72</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1584</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>15.39</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.62</v>
+        <v>16.29</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>12.15</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>6.12</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19">
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>2.34</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1631.58</v>
+        <v>10927.99</v>
       </c>
       <c r="C5" t="n">
-        <v>368953.2</v>
+        <v>2267218.8</v>
       </c>
       <c r="D5" t="n">
-        <v>174462.16</v>
+        <v>1072070.6</v>
       </c>
       <c r="E5" t="n">
-        <v>15287.58</v>
+        <v>118925.46</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32.4</v>
+        <v>1868.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4321.8</v>
+        <v>31777.2</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3239.78</v>
+        <v>17849.66</v>
       </c>
       <c r="C6" t="n">
-        <v>456321.6</v>
+        <v>3265920</v>
       </c>
       <c r="D6" t="n">
-        <v>201976.63</v>
+        <v>1445558.4</v>
       </c>
       <c r="E6" t="n">
-        <v>13384.8</v>
+        <v>129437.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>409.5</v>
+        <v>3142.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4309.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8258.4</v>
+        <v>55222.5</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3023.71</v>
+        <v>30097.2</v>
       </c>
       <c r="C7" t="n">
-        <v>286272</v>
+        <v>4630752</v>
       </c>
       <c r="D7" t="n">
-        <v>143504.06</v>
+        <v>2321329.82</v>
       </c>
       <c r="E7" t="n">
-        <v>9380.07</v>
+        <v>200810.07</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>819</v>
+        <v>12573</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>8957.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8856</v>
+        <v>116208</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1673.46</v>
+        <v>30234.24</v>
       </c>
       <c r="C8" t="n">
-        <v>98280</v>
+        <v>2899512</v>
       </c>
       <c r="D8" t="n">
-        <v>56833.92</v>
+        <v>1676746.37</v>
       </c>
       <c r="E8" t="n">
-        <v>5077.71</v>
+        <v>88528.77</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1540.5</v>
+        <v>45552</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3595.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3876.6</v>
+        <v>110163.6</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>788.58</v>
+        <v>24743.61</v>
       </c>
       <c r="C9" t="n">
-        <v>38304</v>
+        <v>1900584</v>
       </c>
       <c r="D9" t="n">
-        <v>24167.09</v>
+        <v>1199132.75</v>
       </c>
       <c r="E9" t="n">
-        <v>3132.09</v>
+        <v>42403.68</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>969</v>
+        <v>31518</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>850.5</v>
+        <v>71782.2</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>449.37</v>
+        <v>17473.14</v>
       </c>
       <c r="C10" t="n">
-        <v>12096</v>
+        <v>1078056</v>
       </c>
       <c r="D10" t="n">
-        <v>8268.48</v>
+        <v>736928.28</v>
       </c>
       <c r="E10" t="n">
-        <v>522</v>
+        <v>18531</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>690</v>
+        <v>30690</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11959,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>614.1</v>
+        <v>41411.7</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>291.24</v>
+        <v>2873.43</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>206136</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>145524.65</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4425.84</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>4110</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>13050</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>163.98</v>
+        <v>428.85</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>55944</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>40747.21</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>860.4</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>6030</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>129.6</v>
+        <v>183.96</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>13608</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>10152.05</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>141.12</v>
+        <v>144.72</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>2016</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1539.65</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>210</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>15.39</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.62</v>
+        <v>16.29</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>12.15</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>6.12</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
     </row>
     <row r="19">
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>2.34</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3589482.6</v>
+        <v>24041585.7</v>
       </c>
       <c r="C5" t="n">
-        <v>20292426</v>
+        <v>124697034</v>
       </c>
       <c r="D5" t="n">
-        <v>17678250.27</v>
+        <v>108632914.3</v>
       </c>
       <c r="E5" t="n">
-        <v>2816583.74</v>
+        <v>21910826.75</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.36</v>
+        <v>15833.46</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8963.459999999999</v>
+        <v>516892.86</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>139999.2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40711.36</v>
+        <v>299341.22</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7127524.8</v>
+        <v>39269260.8</v>
       </c>
       <c r="C6" t="n">
-        <v>25097688</v>
+        <v>179625600</v>
       </c>
       <c r="D6" t="n">
-        <v>20466292.12</v>
+        <v>146478432.67</v>
       </c>
       <c r="E6" t="n">
-        <v>2466015.55</v>
+        <v>23847491.3</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>70833.89999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>7575.75</v>
+        <v>58136.25</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1192140.18</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>77794.13</v>
+        <v>520195.95</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6652156.5</v>
+        <v>66213833.4</v>
       </c>
       <c r="C7" t="n">
-        <v>15744960</v>
+        <v>254691360</v>
       </c>
       <c r="D7" t="n">
-        <v>14541266.81</v>
+        <v>235220351.07</v>
       </c>
       <c r="E7" t="n">
-        <v>1728184.1</v>
+        <v>36997247.3</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>15151.5</v>
+        <v>232600.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2477981.72</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>83423.52</v>
+        <v>1094679.36</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3681612</v>
+        <v>66515328</v>
       </c>
       <c r="C8" t="n">
-        <v>5405400</v>
+        <v>159473160</v>
       </c>
       <c r="D8" t="n">
-        <v>5758981.11</v>
+        <v>169904709.47</v>
       </c>
       <c r="E8" t="n">
-        <v>935517.29</v>
+        <v>16310540.58</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>28499.25</v>
+        <v>842712</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>994695.08</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>36517.57</v>
+        <v>1037741.11</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1734876</v>
+        <v>54435942</v>
       </c>
       <c r="C9" t="n">
-        <v>2106720</v>
+        <v>104532120</v>
       </c>
       <c r="D9" t="n">
-        <v>2448851.03</v>
+        <v>121508121.35</v>
       </c>
       <c r="E9" t="n">
-        <v>577056.26</v>
+        <v>7812454</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>17926.5</v>
+        <v>583083</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>141091.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8011.71</v>
+        <v>676188.3199999999</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>988614</v>
+        <v>38440908</v>
       </c>
       <c r="C10" t="n">
-        <v>665280</v>
+        <v>59293080</v>
       </c>
       <c r="D10" t="n">
-        <v>837845.08</v>
+        <v>74672942.61</v>
       </c>
       <c r="E10" t="n">
-        <v>96173.28</v>
+        <v>3414151.44</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12765</v>
+        <v>567765</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>116666</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5784.82</v>
+        <v>390098.21</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>640728</v>
+        <v>6321546</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>11337480</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>14746013.19</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>815416.76</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3330</v>
+        <v>76035</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1978.2</v>
+        <v>122931</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>360756</v>
+        <v>943470</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>3076920</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>4128914.99</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>158520.1</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>26640</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>56802.6</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>285120</v>
+        <v>404712</v>
       </c>
       <c r="C13" t="n">
-        <v>27720</v>
+        <v>748440</v>
       </c>
       <c r="D13" t="n">
-        <v>38100.28</v>
+        <v>1028707.63</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>6660</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>29390.4</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>310464</v>
+        <v>318384</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>110880</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>156012.53</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>3885</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>12151.8</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>14058</v>
+        <v>33858</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4804.2</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>3564</v>
+        <v>35838</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>26730</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2543.4</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>3168</v>
+        <v>13464</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4804.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>5148</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5652</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>594</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>249480</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>361140.12</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>68265</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28403.01</v>
+        <v>38543.49</v>
       </c>
       <c r="C4" t="n">
-        <v>5211864</v>
+        <v>4054176</v>
       </c>
       <c r="D4" t="n">
-        <v>4095036</v>
+        <v>3185424</v>
       </c>
       <c r="E4" t="n">
-        <v>1611000</v>
+        <v>1123200</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>83940</v>
+        <v>117240</v>
       </c>
       <c r="H4" t="n">
-        <v>7530</v>
+        <v>14850</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>177840</v>
+        <v>372000</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24284.43</v>
+        <v>13579.38</v>
       </c>
       <c r="C5" t="n">
-        <v>4122216</v>
+        <v>884016</v>
       </c>
       <c r="D5" t="n">
-        <v>3238884</v>
+        <v>694584</v>
       </c>
       <c r="E5" t="n">
-        <v>1078200</v>
+        <v>257400</v>
       </c>
       <c r="F5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>68460</v>
+        <v>35100</v>
       </c>
       <c r="H5" t="n">
-        <v>5190</v>
+        <v>3180</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>151320</v>
+        <v>124680</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>22312.08</v>
+        <v>1347.39</v>
       </c>
       <c r="C6" t="n">
-        <v>3628800</v>
+        <v>117432</v>
       </c>
       <c r="D6" t="n">
-        <v>2851200</v>
+        <v>92268</v>
       </c>
       <c r="E6" t="n">
-        <v>765900</v>
+        <v>34200</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>62850</v>
+        <v>4920</v>
       </c>
       <c r="H6" t="n">
-        <v>7560</v>
+        <v>390</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>149250</v>
+        <v>21540</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31681.26</v>
+        <v>173.61</v>
       </c>
       <c r="C7" t="n">
-        <v>4630752</v>
+        <v>30240</v>
       </c>
       <c r="D7" t="n">
-        <v>3638448</v>
+        <v>23760</v>
       </c>
       <c r="E7" t="n">
-        <v>944100</v>
+        <v>3600</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83820</v>
+        <v>1050</v>
       </c>
       <c r="H7" t="n">
-        <v>12270</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>193680</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>30234.24</v>
+        <v>15.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2899512</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>2278188</v>
+        <v>1188</v>
       </c>
       <c r="E8" t="n">
-        <v>360900</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>70080</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>4230</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>155160</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24743.61</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1900584</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1493316</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>158400</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>37080</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>88620</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17473.14</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1078056</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>847044</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>63900</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30690</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13823,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>46530</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>2873.43</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>206136</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>161964</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4110</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13050</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>428.85</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>55944</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>43956</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>183.96</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13608</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>10692</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>144.72</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1584</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>15.39</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>16.29</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>12.15</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,7 +14135,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10927.99</v>
+        <v>6110.72</v>
       </c>
       <c r="C5" t="n">
-        <v>2267218.8</v>
+        <v>486208.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1072070.6</v>
+        <v>229907.3</v>
       </c>
       <c r="E5" t="n">
-        <v>118925.46</v>
+        <v>28391.22</v>
       </c>
       <c r="F5" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1868.4</v>
+        <v>1144.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>31777.2</v>
+        <v>26182.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>17849.66</v>
+        <v>1077.91</v>
       </c>
       <c r="C6" t="n">
-        <v>3265920</v>
+        <v>105688.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1445558.4</v>
+        <v>46779.88</v>
       </c>
       <c r="E6" t="n">
-        <v>129437.1</v>
+        <v>5779.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3142.5</v>
+        <v>246</v>
       </c>
       <c r="H6" t="n">
-        <v>4309.2</v>
+        <v>222.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>55222.5</v>
+        <v>7969.8</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>30097.2</v>
+        <v>164.93</v>
       </c>
       <c r="C7" t="n">
-        <v>4630752</v>
+        <v>30240</v>
       </c>
       <c r="D7" t="n">
-        <v>2321329.82</v>
+        <v>15158.88</v>
       </c>
       <c r="E7" t="n">
-        <v>200810.07</v>
+        <v>765.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12573</v>
+        <v>157.5</v>
       </c>
       <c r="H7" t="n">
-        <v>8957.1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>116208</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>30234.24</v>
+        <v>15.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2899512</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>1676746.37</v>
+        <v>874.37</v>
       </c>
       <c r="E8" t="n">
-        <v>88528.77</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>45552</v>
+        <v>175.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3595.5</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>110163.6</v>
+        <v>511.2</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24743.61</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1900584</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1199132.75</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>42403.68</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>31518</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>71782.2</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17473.14</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1078056</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>736928.28</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>18531</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>30690</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14755,13 +14749,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>41411.7</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>2873.43</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>206136</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>145524.65</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4425.84</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4110</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>13050</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>428.85</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>55944</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>40747.21</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>860.4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>183.96</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13608</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>10152.05</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>144.72</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>2016</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1539.65</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>15.39</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>16.29</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>12.15</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>6.12</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,7 +15067,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24041585.7</v>
+        <v>13443586.2</v>
       </c>
       <c r="C5" t="n">
-        <v>124697034</v>
+        <v>26741484</v>
       </c>
       <c r="D5" t="n">
-        <v>108632914.3</v>
+        <v>23296507.11</v>
       </c>
       <c r="E5" t="n">
-        <v>21910826.75</v>
+        <v>5230798.37</v>
       </c>
       <c r="F5" t="n">
-        <v>15833.46</v>
+        <v>10000.08</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>516892.86</v>
+        <v>316708.92</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>139999.2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>299341.22</v>
+        <v>246641.98</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>39269260.8</v>
+        <v>2371406.4</v>
       </c>
       <c r="C6" t="n">
-        <v>179625600</v>
+        <v>5812884</v>
       </c>
       <c r="D6" t="n">
-        <v>146478432.67</v>
+        <v>4740204.84</v>
       </c>
       <c r="E6" t="n">
-        <v>23847491.3</v>
+        <v>1064870.35</v>
       </c>
       <c r="F6" t="n">
-        <v>70833.89999999999</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>58136.25</v>
+        <v>4551</v>
       </c>
       <c r="H6" t="n">
-        <v>1192140.18</v>
+        <v>61499.29</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>520195.95</v>
+        <v>75075.52</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>66213833.4</v>
+        <v>362844.9</v>
       </c>
       <c r="C7" t="n">
-        <v>254691360</v>
+        <v>1663200</v>
       </c>
       <c r="D7" t="n">
-        <v>235220351.07</v>
+        <v>1536049.31</v>
       </c>
       <c r="E7" t="n">
-        <v>36997247.3</v>
+        <v>141076.25</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>232600.5</v>
+        <v>2913.75</v>
       </c>
       <c r="H7" t="n">
-        <v>2477981.72</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1094679.36</v>
+        <v>19329.84</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>66515328</v>
+        <v>34254</v>
       </c>
       <c r="C8" t="n">
-        <v>159473160</v>
+        <v>83160</v>
       </c>
       <c r="D8" t="n">
-        <v>169904709.47</v>
+        <v>88599.71000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>16310540.58</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
-        <v>79167.3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>842712</v>
+        <v>3246.75</v>
       </c>
       <c r="H8" t="n">
-        <v>994695.08</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1037741.11</v>
+        <v>4815.5</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>54435942</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>104532120</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>121508121.35</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7812454</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>583083</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>141091.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>676188.3199999999</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>38440908</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>59293080</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>74672942.61</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3414151.44</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>567765</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15687,13 +15681,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>390098.21</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>6321546</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>11337480</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>14746013.19</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>815416.76</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>76035</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>122931</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>943470</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3076920</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4128914.99</v>
-      </c>
-      <c r="E12" t="n">
-        <v>158520.1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>26640</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>56802.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>404712</v>
-      </c>
-      <c r="C13" t="n">
-        <v>748440</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1028707.63</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6660</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>29390.4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>318384</v>
-      </c>
-      <c r="C14" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D14" t="n">
-        <v>156012.53</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>12151.8</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>33858</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>35838</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>26730</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>555</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2543.4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>13464</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>5148</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5652</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>594</v>
-      </c>
-      <c r="C20" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D20" t="n">
-        <v>361140.12</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>68265</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3696.84</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1091664</v>
-      </c>
-      <c r="D4" t="n">
-        <v>857736</v>
-      </c>
-      <c r="E4" t="n">
-        <v>384300</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13260</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3990</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>33330</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4609.26</v>
-      </c>
-      <c r="C5" t="n">
-        <v>975240</v>
-      </c>
-      <c r="D5" t="n">
-        <v>766260</v>
-      </c>
-      <c r="E5" t="n">
-        <v>228600</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16050</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2910</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>34800</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4486.41</v>
-      </c>
-      <c r="C6" t="n">
-        <v>590688</v>
-      </c>
-      <c r="D6" t="n">
-        <v>464112</v>
-      </c>
-      <c r="E6" t="n">
-        <v>122400</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12990</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>25710</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3831.21</v>
-      </c>
-      <c r="C7" t="n">
-        <v>338688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>266112</v>
-      </c>
-      <c r="E7" t="n">
-        <v>67500</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5010</v>
-      </c>
-      <c r="H7" t="n">
-        <v>510</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14820</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4233.78</v>
-      </c>
-      <c r="C8" t="n">
-        <v>272160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>213840</v>
-      </c>
-      <c r="E8" t="n">
-        <v>38700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3210</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>11490</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4122.81</v>
-      </c>
-      <c r="C9" t="n">
-        <v>197064</v>
-      </c>
-      <c r="D9" t="n">
-        <v>154836</v>
-      </c>
-      <c r="E9" t="n">
-        <v>30600</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3900</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10380</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3118.05</v>
-      </c>
-      <c r="C10" t="n">
-        <v>123984</v>
-      </c>
-      <c r="D10" t="n">
-        <v>97416</v>
-      </c>
-      <c r="E10" t="n">
-        <v>10800</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3570</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8220</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2170.53</v>
-      </c>
-      <c r="C11" t="n">
-        <v>45864</v>
-      </c>
-      <c r="D11" t="n">
-        <v>36036</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>780</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1221.21</v>
-      </c>
-      <c r="C12" t="n">
-        <v>14616</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11484</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>718.11</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>451.62</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3168</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>353.7</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>311.67</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>404.64</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>172.89</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2074.17</v>
-      </c>
-      <c r="C5" t="n">
-        <v>536382</v>
-      </c>
-      <c r="D5" t="n">
-        <v>253632.06</v>
-      </c>
-      <c r="E5" t="n">
-        <v>25214.58</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1047.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7308</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3589.13</v>
-      </c>
-      <c r="C6" t="n">
-        <v>531619.2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>235304.78</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20685.6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>649.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>615.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9512.700000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3639.65</v>
-      </c>
-      <c r="C7" t="n">
-        <v>338688</v>
-      </c>
-      <c r="D7" t="n">
-        <v>169779.46</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14357.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>751.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>372.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8892</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4233.78</v>
-      </c>
-      <c r="C8" t="n">
-        <v>272160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>157386.24</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9493.110000000001</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2086.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8157.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4122.81</v>
-      </c>
-      <c r="C9" t="n">
-        <v>197064</v>
-      </c>
-      <c r="D9" t="n">
-        <v>124333.31</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8191.62</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3315</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8407.799999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3118.05</v>
-      </c>
-      <c r="C10" t="n">
-        <v>123984</v>
-      </c>
-      <c r="D10" t="n">
-        <v>84751.92</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3132</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3570</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7315.8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2170.53</v>
-      </c>
-      <c r="C11" t="n">
-        <v>45864</v>
-      </c>
-      <c r="D11" t="n">
-        <v>32378.35</v>
-      </c>
-      <c r="E11" t="n">
-        <v>737.64</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>780</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1221.21</v>
-      </c>
-      <c r="C12" t="n">
-        <v>14616</v>
-      </c>
-      <c r="D12" t="n">
-        <v>10645.67</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>718.11</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2632.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>476.28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>451.62</v>
-      </c>
-      <c r="C14" t="n">
-        <v>4032</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3079.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>353.7</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>311.67</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>404.64</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>172.89</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4563167.4</v>
-      </c>
-      <c r="C5" t="n">
-        <v>29501010</v>
-      </c>
-      <c r="D5" t="n">
-        <v>25700536.64</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4645534.22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6666.72</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>289818.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>68841.36</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7896081.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>29239056</v>
-      </c>
-      <c r="D6" t="n">
-        <v>23843433.76</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3811114.94</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12015.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>170305.74</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>89609.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8007228.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18627840</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17203752.28</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2645179.74</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13902.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>102996.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>83762.64</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9314316</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14968800</v>
-      </c>
-      <c r="D8" t="n">
-        <v>15947947.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1749010.59</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>38600.25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>76847.42</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>9070182</v>
-      </c>
-      <c r="C9" t="n">
-        <v>10838520</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12598694.1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1509224.07</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>61327.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>79201.48</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>6859710</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6819120</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8587912.050000001</v>
-      </c>
-      <c r="E10" t="n">
-        <v>577039.6800000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>66045</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>68914.84</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4775166</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2522520</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3280897.8</v>
-      </c>
-      <c r="E11" t="n">
-        <v>135902.79</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>14430</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>18934.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2686662</v>
-      </c>
-      <c r="C12" t="n">
-        <v>803880</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1078725.54</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6105</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4239</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1579842</v>
-      </c>
-      <c r="C13" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D13" t="n">
-        <v>266701.98</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87749.83</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>993564</v>
-      </c>
-      <c r="C14" t="n">
-        <v>221760</v>
-      </c>
-      <c r="D14" t="n">
-        <v>312025.06</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>778140</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>685674</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>890208</v>
-      </c>
-      <c r="C17" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D17" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>380358</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>85338</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>44946</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>38543.49</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4054176</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3185424</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1123200</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" t="n">
-        <v>117240</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14850</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>372000</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13579.38</v>
-      </c>
-      <c r="C5" t="n">
-        <v>884016</v>
-      </c>
-      <c r="D5" t="n">
-        <v>694584</v>
-      </c>
-      <c r="E5" t="n">
-        <v>257400</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>35100</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3180</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>124680</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1347.39</v>
-      </c>
-      <c r="C6" t="n">
-        <v>117432</v>
-      </c>
-      <c r="D6" t="n">
-        <v>92268</v>
-      </c>
-      <c r="E6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4920</v>
-      </c>
-      <c r="H6" t="n">
-        <v>390</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21540</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>173.61</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30240</v>
-      </c>
-      <c r="D7" t="n">
-        <v>23760</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6110.72</v>
-      </c>
-      <c r="C5" t="n">
-        <v>486208.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>229907.3</v>
-      </c>
-      <c r="E5" t="n">
-        <v>28391.22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1144.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26182.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1077.91</v>
-      </c>
-      <c r="C6" t="n">
-        <v>105688.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>46779.88</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5779.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>246</v>
-      </c>
-      <c r="H6" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7969.8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>164.93</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30240</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15158.88</v>
-      </c>
-      <c r="E7" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D8" t="n">
-        <v>874.37</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>511.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13443586.2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>26741484</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23296507.11</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5230798.37</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10000.08</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>316708.92</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>246641.98</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2371406.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5812884</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4740204.84</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1064870.35</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4551</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61499.29</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75075.52</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>362844.9</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1663200</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1536049.31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>141076.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2913.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>19329.84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>34254</v>
-      </c>
-      <c r="C8" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88599.71000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3246.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4815.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
@@ -538,7 +538,7 @@
         <v>64260</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -576,7 +576,7 @@
         <v>54660</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -614,7 +614,7 @@
         <v>43050</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>15</v>
@@ -652,7 +652,7 @@
         <v>47370</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -690,7 +690,7 @@
         <v>30660</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>12</v>
@@ -728,7 +728,7 @@
         <v>12180</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>6</v>
@@ -766,7 +766,7 @@
         <v>3780</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -804,7 +804,7 @@
         <v>4230</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -842,7 +842,7 @@
         <v>5670</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -918,7 +918,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>2880</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>3690</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         <v>5610</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>2880</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -2668,7 +2668,7 @@
         <v>3690</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         <v>5610</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>796752</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>291665</v>
@@ -3600,7 +3600,7 @@
         <v>1020838.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3638,7 +3638,7 @@
         <v>1552006.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>58333</v>
@@ -3714,7 +3714,7 @@
         <v>207487.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>7530</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>5190</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -9934,7 +9934,7 @@
         <v>7560</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -9972,7 +9972,7 @@
         <v>12270</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10010,7 +10010,7 @@
         <v>4230</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19677.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="J5" t="n">
         <v>6.6</v>
@@ -10866,7 +10866,7 @@
         <v>24538.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
@@ -10904,7 +10904,7 @@
         <v>34580.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -10942,7 +10942,7 @@
         <v>26061</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>10.2</v>
@@ -10980,7 +10980,7 @@
         <v>12180</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>5.7</v>
@@ -11018,7 +11018,7 @@
         <v>3780</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
         <v>4230</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>4</v>
@@ -11094,7 +11094,7 @@
         <v>5670</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -11170,7 +11170,7 @@
         <v>750</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>1868.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -11798,7 +11798,7 @@
         <v>4309.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>8957.1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11874,7 +11874,7 @@
         <v>3595.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -11988,7 +11988,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>516892.86</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>287497.5</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>
@@ -12730,7 +12730,7 @@
         <v>1192140.18</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -12768,7 +12768,7 @@
         <v>2477981.72</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12806,7 +12806,7 @@
         <v>994695.08</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -12920,7 +12920,7 @@
         <v>8299.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>14850</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -16420,7 +16420,7 @@
         <v>5443808.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>402496.5</v>
       </c>
       <c r="J5" t="n">
         <v>384997.8</v>
@@ -16458,7 +16458,7 @@
         <v>6788576.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>437497.5</v>
@@ -16496,7 +16496,7 @@
         <v>9566584.66</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>408331</v>
@@ -16534,7 +16534,7 @@
         <v>7209775.65</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>594996.6</v>
@@ -16572,7 +16572,7 @@
         <v>3369597</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>332498.1</v>
@@ -16610,7 +16610,7 @@
         <v>1045737</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>583330</v>
@@ -16648,7 +16648,7 @@
         <v>1170229.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>233332</v>
@@ -16686,7 +16686,7 @@
         <v>1568605.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>116666</v>
@@ -16762,7 +16762,7 @@
         <v>207487.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>2850</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -17352,7 +17352,7 @@
         <v>6600</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -17504,7 +17504,7 @@
         <v>7080</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
@@ -18284,7 +18284,7 @@
         <v>2376</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
@@ -18436,7 +18436,7 @@
         <v>7080</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>2.85</v>
@@ -19216,7 +19216,7 @@
         <v>657320.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>34999.8</v>
@@ -19368,7 +19368,7 @@
         <v>1958682</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>166249.05</v>
@@ -20110,7 +20110,7 @@
         <v>16080</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>12</v>
@@ -20148,7 +20148,7 @@
         <v>22860</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -21080,7 +21080,7 @@
         <v>8229.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -22012,7 +22012,7 @@
         <v>2276718.84</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
@@ -544,7 +544,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1174</v>
       </c>
       <c r="L4" t="n">
         <v>1468680</v>
@@ -582,7 +582,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="L5" t="n">
         <v>921810</v>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>412</v>
       </c>
       <c r="L6" t="n">
         <v>579570</v>
@@ -658,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>462</v>
       </c>
       <c r="L7" t="n">
         <v>542640</v>
@@ -696,7 +696,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="L8" t="n">
         <v>469020</v>
@@ -734,7 +734,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
         <v>394950</v>
@@ -772,7 +772,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="L10" t="n">
         <v>322410</v>
@@ -810,7 +810,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="L11" t="n">
         <v>202590</v>
@@ -848,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
         <v>153990</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L13" t="n">
         <v>119670</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>48810</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
         <v>23730</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>9630</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>17010</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>20220</v>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L6" t="n">
         <v>20040</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
         <v>24840</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>35550</v>
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>41880</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>45540</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>49320</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
         <v>83880</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L13" t="n">
         <v>84660</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
         <v>38250</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>18390</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>8280</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -2446,7 +2446,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="L5" t="n">
         <v>4246.2</v>
@@ -2484,7 +2484,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>12.35</v>
       </c>
       <c r="L6" t="n">
         <v>7414.8</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>15.58</v>
       </c>
       <c r="L7" t="n">
         <v>14904</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="L8" t="n">
         <v>25240.5</v>
@@ -2598,7 +2598,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L9" t="n">
         <v>33922.8</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L10" t="n">
         <v>40530.6</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L11" t="n">
         <v>49320</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L12" t="n">
         <v>83880</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L13" t="n">
         <v>84660</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L14" t="n">
         <v>38250</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L15" t="n">
         <v>18390</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>8280</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -3378,7 +3378,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71682.24000000001</v>
       </c>
       <c r="L5" t="n">
         <v>39999.2</v>
@@ -3416,7 +3416,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>263474.9</v>
       </c>
       <c r="L6" t="n">
         <v>69847.42</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>332383.72</v>
       </c>
       <c r="L7" t="n">
         <v>140395.68</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>307209.6</v>
       </c>
       <c r="L8" t="n">
         <v>237765.51</v>
@@ -3530,7 +3530,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L9" t="n">
         <v>319552.78</v>
@@ -3568,7 +3568,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>490682</v>
       </c>
       <c r="L10" t="n">
         <v>381798.25</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L11" t="n">
         <v>464594.4</v>
@@ -3644,7 +3644,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>789358</v>
       </c>
       <c r="L12" t="n">
         <v>790149.6</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>810692</v>
       </c>
       <c r="L13" t="n">
         <v>797497.2</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>533350</v>
       </c>
       <c r="L14" t="n">
         <v>360315</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L15" t="n">
         <v>173233.8</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L16" t="n">
         <v>77997.60000000001</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>23455.8</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>153120</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>62220</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>12750</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>3270</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="L5" t="n">
         <v>13066.2</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>4717.5</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1962</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>277768.68</v>
       </c>
       <c r="L5" t="n">
         <v>123083.6</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>44438.85</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>18482.04</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L4" t="n">
         <v>150180</v>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
         <v>53670</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
         <v>16590</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>4620</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2520</v>
@@ -8038,7 +8038,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>23.94</v>
       </c>
       <c r="L5" t="n">
         <v>11270.7</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
         <v>6138.3</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>2772</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1789.2</v>
@@ -8970,7 +8970,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>510735.96</v>
       </c>
       <c r="L5" t="n">
         <v>106169.99</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>138671</v>
       </c>
       <c r="L6" t="n">
         <v>57822.79</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>26112.24</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>16854.26</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="L4" t="n">
         <v>177840</v>
@@ -9902,7 +9902,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="L5" t="n">
         <v>151320</v>
@@ -9940,7 +9940,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L6" t="n">
         <v>149250</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L7" t="n">
         <v>193680</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L8" t="n">
         <v>155160</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
         <v>88620</v>
@@ -10092,7 +10092,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
         <v>46530</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>13050</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>6030</v>
@@ -10834,7 +10834,7 @@
         <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>274.68</v>
       </c>
       <c r="L5" t="n">
         <v>193580.1</v>
@@ -10872,7 +10872,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>267.8</v>
       </c>
       <c r="L6" t="n">
         <v>214440.9</v>
@@ -10910,7 +10910,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>378.84</v>
       </c>
       <c r="L7" t="n">
         <v>325584</v>
@@ -10948,7 +10948,7 @@
         <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>344.7</v>
       </c>
       <c r="L8" t="n">
         <v>333004.2</v>
@@ -10986,7 +10986,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="L9" t="n">
         <v>319909.5</v>
@@ -11024,7 +11024,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="L10" t="n">
         <v>286944.9</v>
@@ -11062,7 +11062,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="L11" t="n">
         <v>202590</v>
@@ -11100,7 +11100,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="L12" t="n">
         <v>153990</v>
@@ -11138,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L13" t="n">
         <v>119670</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>48810</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L15" t="n">
         <v>23730</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>9630</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -11766,7 +11766,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.56</v>
       </c>
       <c r="L5" t="n">
         <v>31777.2</v>
@@ -11804,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>86.45</v>
       </c>
       <c r="L6" t="n">
         <v>55222.5</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>164.82</v>
       </c>
       <c r="L7" t="n">
         <v>116208</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>137.7</v>
       </c>
       <c r="L8" t="n">
         <v>110163.6</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
         <v>71782.2</v>
@@ -11956,7 +11956,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="L10" t="n">
         <v>41411.7</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
         <v>13050</v>
@@ -12032,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>6030</v>
@@ -12698,7 +12698,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1505327.04</v>
       </c>
       <c r="L5" t="n">
         <v>299341.22</v>
@@ -12736,7 +12736,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1844324.3</v>
       </c>
       <c r="L6" t="n">
         <v>520195.95</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3516269.88</v>
       </c>
       <c r="L7" t="n">
         <v>1094679.36</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2937691.8</v>
       </c>
       <c r="L8" t="n">
         <v>1037741.11</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2112066</v>
       </c>
       <c r="L9" t="n">
         <v>676188.3199999999</v>
@@ -12888,7 +12888,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1237372</v>
       </c>
       <c r="L10" t="n">
         <v>390098.21</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>234674</v>
       </c>
       <c r="L11" t="n">
         <v>122931</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L12" t="n">
         <v>56802.6</v>
@@ -13592,7 +13592,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
         <v>372000</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>124680</v>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>21540</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="L5" t="n">
         <v>26182.8</v>
@@ -14600,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>7969.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>304649.52</v>
       </c>
       <c r="L5" t="n">
         <v>246641.98</v>
@@ -15532,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>75075.52</v>
@@ -16426,7 +16426,7 @@
         <v>384997.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5860023.12</v>
       </c>
       <c r="L5" t="n">
         <v>1823524.54</v>
@@ -16464,7 +16464,7 @@
         <v>437497.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5713245.2</v>
       </c>
       <c r="L6" t="n">
         <v>2020033.28</v>
@@ -16502,7 +16502,7 @@
         <v>408331</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>8082172.56</v>
       </c>
       <c r="L7" t="n">
         <v>3067001.28</v>
@@ -16540,7 +16540,7 @@
         <v>594996.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7353829.8</v>
       </c>
       <c r="L8" t="n">
         <v>3136899.56</v>
@@ -16578,7 +16578,7 @@
         <v>332498.1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7360230</v>
       </c>
       <c r="L9" t="n">
         <v>3013547.49</v>
@@ -16616,7 +16616,7 @@
         <v>583330</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6229528</v>
       </c>
       <c r="L10" t="n">
         <v>2703020.96</v>
@@ -16654,7 +16654,7 @@
         <v>233332</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4032126</v>
       </c>
       <c r="L11" t="n">
         <v>1908397.8</v>
@@ -16692,7 +16692,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2496078</v>
       </c>
       <c r="L12" t="n">
         <v>1450585.8</v>
@@ -16730,7 +16730,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1429378</v>
       </c>
       <c r="L13" t="n">
         <v>1127291.4</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>725356</v>
       </c>
       <c r="L14" t="n">
         <v>459790.2</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>298676</v>
       </c>
       <c r="L15" t="n">
         <v>223536.6</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L16" t="n">
         <v>90714.60000000001</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L17" t="n">
         <v>29390.4</v>
@@ -17320,7 +17320,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="L4" t="n">
         <v>134430</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
         <v>164700</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L6" t="n">
         <v>161940</v>
@@ -17434,7 +17434,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="L7" t="n">
         <v>180150</v>
@@ -17472,7 +17472,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="L8" t="n">
         <v>219240</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="L9" t="n">
         <v>246420</v>
@@ -17548,7 +17548,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L10" t="n">
         <v>219600</v>
@@ -17586,7 +17586,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L11" t="n">
         <v>137160</v>
@@ -17624,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
         <v>63030</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L13" t="n">
         <v>31740</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>8730</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>360</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>61.74</v>
       </c>
       <c r="L5" t="n">
         <v>34587</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>86.45</v>
       </c>
       <c r="L6" t="n">
         <v>59917.8</v>
@@ -18366,7 +18366,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>125.46</v>
       </c>
       <c r="L7" t="n">
         <v>108090</v>
@@ -18404,7 +18404,7 @@
         <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>168.3</v>
       </c>
       <c r="L8" t="n">
         <v>155660.4</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="L9" t="n">
         <v>199600.2</v>
@@ -18480,7 +18480,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L10" t="n">
         <v>195444</v>
@@ -18518,7 +18518,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L11" t="n">
         <v>137160</v>
@@ -18556,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L12" t="n">
         <v>63030</v>
@@ -18594,7 +18594,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="L13" t="n">
         <v>31740</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
         <v>8730</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>360</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1317161.16</v>
       </c>
       <c r="L5" t="n">
         <v>325809.54</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1844324.3</v>
       </c>
       <c r="L6" t="n">
         <v>564425.6800000001</v>
@@ -19298,7 +19298,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2676563.64</v>
       </c>
       <c r="L7" t="n">
         <v>1018207.8</v>
@@ -19336,7 +19336,7 @@
         <v>545413.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3590512.2</v>
       </c>
       <c r="L8" t="n">
         <v>1466320.97</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4650812</v>
       </c>
       <c r="L9" t="n">
         <v>1880233.88</v>
@@ -19412,7 +19412,7 @@
         <v>174999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4480140</v>
       </c>
       <c r="L10" t="n">
         <v>1841082.48</v>
@@ -19450,7 +19450,7 @@
         <v>174999</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3242768</v>
       </c>
       <c r="L11" t="n">
         <v>1292047.2</v>
@@ -19488,7 +19488,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1642718</v>
       </c>
       <c r="L12" t="n">
         <v>593742.6</v>
@@ -19526,7 +19526,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>597352</v>
       </c>
       <c r="L13" t="n">
         <v>298990.8</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>192006</v>
       </c>
       <c r="L14" t="n">
         <v>82236.60000000001</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L15" t="n">
         <v>45498.6</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>9891</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>3391.2</v>
@@ -20116,7 +20116,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
         <v>406950</v>
@@ -20154,7 +20154,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="L5" t="n">
         <v>285420</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="L6" t="n">
         <v>142350</v>
@@ -20230,7 +20230,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L7" t="n">
         <v>94860</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
         <v>36600</v>
@@ -20306,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>5880</v>
@@ -21086,7 +21086,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>87.78</v>
       </c>
       <c r="L5" t="n">
         <v>59938.2</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
       <c r="L6" t="n">
         <v>52669.5</v>
@@ -21162,7 +21162,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>68.88</v>
       </c>
       <c r="L7" t="n">
         <v>56916</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="L8" t="n">
         <v>25986</v>
@@ -21238,7 +21238,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>4762.8</v>
@@ -22018,7 +22018,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1872698.52</v>
       </c>
       <c r="L5" t="n">
         <v>564617.84</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1553115.2</v>
       </c>
       <c r="L6" t="n">
         <v>496146.69</v>
@@ -22094,7 +22094,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1469485.92</v>
       </c>
       <c r="L7" t="n">
         <v>536148.72</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>460814.4</v>
       </c>
       <c r="L8" t="n">
         <v>244788.12</v>
@@ -22170,7 +22170,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>44865.58</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
@@ -549,7 +549,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>1159</v>
+        <v>449</v>
       </c>
       <c r="L4" t="n">
         <v>1465470</v>
@@ -590,7 +590,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>267</v>
       </c>
       <c r="L5" t="n">
         <v>919950</v>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>404</v>
+        <v>155</v>
       </c>
       <c r="L6" t="n">
         <v>577740</v>
@@ -672,7 +672,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>461</v>
+        <v>176</v>
       </c>
       <c r="L7" t="n">
         <v>541590</v>
@@ -713,7 +713,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="L8" t="n">
         <v>468300</v>
@@ -754,7 +754,7 @@
         <v>6</v>
       </c>
       <c r="K9" t="n">
-        <v>345</v>
+        <v>108</v>
       </c>
       <c r="L9" t="n">
         <v>394590</v>
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>292</v>
+        <v>75</v>
       </c>
       <c r="L10" t="n">
         <v>322320</v>
@@ -836,7 +836,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>189</v>
+        <v>41</v>
       </c>
       <c r="L11" t="n">
         <v>202320</v>
@@ -877,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>117</v>
+        <v>17</v>
       </c>
       <c r="L12" t="n">
         <v>153780</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="L13" t="n">
         <v>119670</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>48810</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>23730</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>9630</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>17010</v>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>20190</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>20070</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="L7" t="n">
         <v>24930</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>35730</v>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>42090</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>45570</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>49470</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>84090</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>84690</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>38310</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>18450</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8280</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -2598,7 +2598,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.32</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="n">
         <v>4239.9</v>
@@ -2639,7 +2639,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9.630000000000001</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>7425.9</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.12</v>
+        <v>5.74</v>
       </c>
       <c r="L7" t="n">
         <v>14958</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>11.78</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
         <v>25368.3</v>
@@ -2762,7 +2762,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>18.47</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>34092.9</v>
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>20.01</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
         <v>40557.3</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>23.36</v>
+        <v>2.7</v>
       </c>
       <c r="L11" t="n">
         <v>49470</v>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>34.3</v>
+        <v>4.64</v>
       </c>
       <c r="L12" t="n">
         <v>84090</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>36.08</v>
+        <v>6.65</v>
       </c>
       <c r="L13" t="n">
         <v>84690</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24.3</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>38310</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>11.83</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>18450</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8280</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>2490</v>
@@ -3602,7 +3602,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>112504.25</v>
+        <v>48216.11</v>
       </c>
       <c r="L5" t="n">
         <v>763182</v>
@@ -3643,7 +3643,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>467739.95</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
         <v>1336662</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>588595.83</v>
+        <v>278808.55</v>
       </c>
       <c r="L7" t="n">
         <v>2692440</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>571795.46</v>
+        <v>321634.94</v>
       </c>
       <c r="L8" t="n">
         <v>4566294</v>
@@ -3766,7 +3766,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>896780.76</v>
+        <v>467885.62</v>
       </c>
       <c r="L9" t="n">
         <v>6136722</v>
@@ -3807,7 +3807,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>971605.5600000001</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
         <v>7300314</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1134316.72</v>
+        <v>130882.7</v>
       </c>
       <c r="L11" t="n">
         <v>8904600</v>
@@ -3889,7 +3889,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>1665422.24</v>
+        <v>225057.06</v>
       </c>
       <c r="L12" t="n">
         <v>15136200</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1751949.04</v>
+        <v>322727.45</v>
       </c>
       <c r="L13" t="n">
         <v>15244200</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1179910.8</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>6895800</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>574514.59</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3321000</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1490400</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>448200</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
         <v>153060</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>62910</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>12690</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.26</v>
+        <v>5.96</v>
       </c>
       <c r="L5" t="n">
         <v>13211.1</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4695.3</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>498233.12</v>
+        <v>289296.65</v>
       </c>
       <c r="L5" t="n">
         <v>2377998</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>845154</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>191</v>
+        <v>39</v>
       </c>
       <c r="L4" t="n">
         <v>150270</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>54240</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>16860</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4590</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2520</v>
@@ -8622,7 +8622,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>18.87</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>11390.4</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>6238.2</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2754</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1789.2</v>
@@ -9626,7 +9626,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>916106.05</v>
+        <v>208936.47</v>
       </c>
       <c r="L5" t="n">
         <v>2050272</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>246178.92</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1122876</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>495720</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>322056</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>230</v>
+        <v>132</v>
       </c>
       <c r="L4" t="n">
         <v>178290</v>
@@ -10630,7 +10630,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>168</v>
+        <v>95</v>
       </c>
       <c r="L5" t="n">
         <v>151410</v>
@@ -10671,7 +10671,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="L6" t="n">
         <v>149340</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>201</v>
+        <v>85</v>
       </c>
       <c r="L7" t="n">
         <v>193710</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>48</v>
       </c>
       <c r="L8" t="n">
         <v>155250</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="L9" t="n">
         <v>88680</v>
@@ -10835,7 +10835,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
         <v>46530</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>13050</v>
@@ -11634,7 +11634,7 @@
         <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>210.85</v>
+        <v>88.38</v>
       </c>
       <c r="L5" t="n">
         <v>193189.5</v>
@@ -11675,7 +11675,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>204.83</v>
+        <v>78.59</v>
       </c>
       <c r="L6" t="n">
         <v>213763.8</v>
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>294.12</v>
+        <v>112.29</v>
       </c>
       <c r="L7" t="n">
         <v>324954</v>
@@ -11757,7 +11757,7 @@
         <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>281.89</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>332493</v>
@@ -11798,7 +11798,7 @@
         <v>5.7</v>
       </c>
       <c r="K9" t="n">
-        <v>277.04</v>
+        <v>86.72</v>
       </c>
       <c r="L9" t="n">
         <v>319617.9</v>
@@ -11839,7 +11839,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>254.04</v>
+        <v>65.25</v>
       </c>
       <c r="L10" t="n">
         <v>286864.8</v>
@@ -11880,7 +11880,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>169.82</v>
+        <v>36.84</v>
       </c>
       <c r="L11" t="n">
         <v>202320</v>
@@ -11921,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>108.46</v>
+        <v>15.76</v>
       </c>
       <c r="L12" t="n">
         <v>153780</v>
@@ -11962,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>63.62</v>
+        <v>7.6</v>
       </c>
       <c r="L13" t="n">
         <v>119670</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>33.05</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>48810</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>23730</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>9630</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -12638,7 +12638,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>55.61</v>
+        <v>31.44</v>
       </c>
       <c r="L5" t="n">
         <v>31796.1</v>
@@ -12679,7 +12679,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>67.43000000000001</v>
+        <v>31.94</v>
       </c>
       <c r="L6" t="n">
         <v>55255.8</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>128.24</v>
+        <v>54.23</v>
       </c>
       <c r="L7" t="n">
         <v>116226</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>112.61</v>
+        <v>35.33</v>
       </c>
       <c r="L8" t="n">
         <v>110227.5</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>79.5</v>
+        <v>28.1</v>
       </c>
       <c r="L9" t="n">
         <v>71830.8</v>
@@ -12843,7 +12843,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>51.33</v>
+        <v>12.18</v>
       </c>
       <c r="L10" t="n">
         <v>41411.7</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>9.880000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>13050</v>
@@ -13642,7 +13642,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2700102.05</v>
+        <v>1526843.42</v>
       </c>
       <c r="L5" t="n">
         <v>5723298</v>
@@ -13683,7 +13683,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>3274179.64</v>
+        <v>1550927.2</v>
       </c>
       <c r="L6" t="n">
         <v>9946044</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>6226724.33</v>
+        <v>2633191.88</v>
       </c>
       <c r="L7" t="n">
         <v>20920680</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5467794.05</v>
+        <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
         <v>19840950</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3860056.33</v>
+        <v>1364666.38</v>
       </c>
       <c r="L9" t="n">
         <v>12929544</v>
@@ -13847,7 +13847,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2492379.48</v>
+        <v>591412.08</v>
       </c>
       <c r="L10" t="n">
         <v>7454106</v>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>479903.23</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>2349000</v>
@@ -14605,7 +14605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
         <v>374580</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>125790</v>
@@ -14687,7 +14687,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>21270</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.25</v>
+        <v>5.63</v>
       </c>
       <c r="L5" t="n">
         <v>26415.9</v>
@@ -15691,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7869.9</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>546449.22</v>
+        <v>273224.61</v>
       </c>
       <c r="L5" t="n">
         <v>4754862</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1416582</v>
@@ -17658,7 +17658,7 @@
         <v>160234.8</v>
       </c>
       <c r="K5" t="n">
-        <v>10237886.93</v>
+        <v>4291233.61</v>
       </c>
       <c r="L5" t="n">
         <v>34774110</v>
@@ -17699,7 +17699,7 @@
         <v>182085</v>
       </c>
       <c r="K6" t="n">
-        <v>9945628.369999999</v>
+        <v>3815773.26</v>
       </c>
       <c r="L6" t="n">
         <v>38477484</v>
@@ -17740,7 +17740,7 @@
         <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>14281193.61</v>
+        <v>5452256.13</v>
       </c>
       <c r="L7" t="n">
         <v>58491720</v>
@@ -17781,7 +17781,7 @@
         <v>247635.6</v>
       </c>
       <c r="K8" t="n">
-        <v>13687353.73</v>
+        <v>3859619.33</v>
       </c>
       <c r="L8" t="n">
         <v>59848740</v>
@@ -17822,7 +17822,7 @@
         <v>138384.6</v>
       </c>
       <c r="K9" t="n">
-        <v>13451711.46</v>
+        <v>4210970.54</v>
       </c>
       <c r="L9" t="n">
         <v>57531222</v>
@@ -17863,7 +17863,7 @@
         <v>242780</v>
       </c>
       <c r="K10" t="n">
-        <v>12335166.24</v>
+        <v>3168279</v>
       </c>
       <c r="L10" t="n">
         <v>51635664</v>
@@ -17904,7 +17904,7 @@
         <v>97112</v>
       </c>
       <c r="K11" t="n">
-        <v>8245609.97</v>
+        <v>1788730.21</v>
       </c>
       <c r="L11" t="n">
         <v>36417600</v>
@@ -17945,7 +17945,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>5266335.2</v>
+        <v>765194</v>
       </c>
       <c r="L12" t="n">
         <v>27680400</v>
@@ -17986,7 +17986,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>3088962.77</v>
+        <v>368831.38</v>
       </c>
       <c r="L13" t="n">
         <v>21540600</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1604678.69</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>8785800</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>670267.02</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4271400</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1733400</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>561600</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>131430</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="L5" t="n">
         <v>163200</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="L6" t="n">
         <v>161250</v>
@@ -18744,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="L7" t="n">
         <v>179310</v>
@@ -18785,7 +18785,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>187</v>
+        <v>50</v>
       </c>
       <c r="L8" t="n">
         <v>218640</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>218</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
         <v>246060</v>
@@ -18867,7 +18867,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>210</v>
+        <v>57</v>
       </c>
       <c r="L10" t="n">
         <v>219570</v>
@@ -18908,7 +18908,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="L11" t="n">
         <v>137010</v>
@@ -18949,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
         <v>62820</v>
@@ -18990,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>31800</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>8760</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>360</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>43.36</v>
+        <v>22.18</v>
       </c>
       <c r="L5" t="n">
         <v>34272</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>63.38</v>
+        <v>24.34</v>
       </c>
       <c r="L6" t="n">
         <v>59662.5</v>
@@ -19748,7 +19748,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>96.98</v>
+        <v>40.83</v>
       </c>
       <c r="L7" t="n">
         <v>107586</v>
@@ -19789,7 +19789,7 @@
         <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>137.63</v>
+        <v>36.8</v>
       </c>
       <c r="L8" t="n">
         <v>155234.4</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>175.05</v>
+        <v>48.18</v>
       </c>
       <c r="L9" t="n">
         <v>199308.6</v>
@@ -19871,7 +19871,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>182.7</v>
+        <v>49.59</v>
       </c>
       <c r="L10" t="n">
         <v>195417.3</v>
@@ -19912,7 +19912,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>136.57</v>
+        <v>33.24</v>
       </c>
       <c r="L11" t="n">
         <v>137010</v>
@@ -19953,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>71.38</v>
+        <v>8.34</v>
       </c>
       <c r="L12" t="n">
         <v>62820</v>
@@ -19994,7 +19994,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>27.54</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>31800</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>8760</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4830</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>360</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2105436.72</v>
+        <v>1076826.41</v>
       </c>
       <c r="L5" t="n">
         <v>6168960</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>3077236.5</v>
+        <v>1181658.82</v>
       </c>
       <c r="L6" t="n">
         <v>10739250</v>
@@ -20752,7 +20752,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4708766.66</v>
+        <v>1982638.59</v>
       </c>
       <c r="L7" t="n">
         <v>19365480</v>
@@ -20793,7 +20793,7 @@
         <v>226999.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6682859.39</v>
+        <v>1786860.8</v>
       </c>
       <c r="L8" t="n">
         <v>27942192</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8499922.02</v>
+        <v>2339428.08</v>
       </c>
       <c r="L9" t="n">
         <v>35875548</v>
@@ -20875,7 +20875,7 @@
         <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>8871181.199999999</v>
+        <v>2407892.04</v>
       </c>
       <c r="L10" t="n">
         <v>35175114</v>
@@ -20916,7 +20916,7 @@
         <v>72834</v>
       </c>
       <c r="K11" t="n">
-        <v>6631390.03</v>
+        <v>1614219.94</v>
       </c>
       <c r="L11" t="n">
         <v>24661800</v>
@@ -20957,7 +20957,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>3465878.72</v>
+        <v>405102.71</v>
       </c>
       <c r="L12" t="n">
         <v>11307600</v>
@@ -20998,7 +20998,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1337013.74</v>
+        <v>46103.92</v>
       </c>
       <c r="L13" t="n">
         <v>5724000</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>424767.89</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1576800</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>95752.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>869400</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>189000</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>64800</v>
@@ -21633,7 +21633,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>107</v>
       </c>
       <c r="L4" t="n">
         <v>405750</v>
@@ -21674,7 +21674,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
         <v>284310</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>112</v>
+        <v>36</v>
       </c>
       <c r="L6" t="n">
         <v>142830</v>
@@ -21756,7 +21756,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="L7" t="n">
         <v>94830</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>36750</v>
@@ -21838,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>5850</v>
@@ -22678,7 +22678,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>69.18000000000001</v>
+        <v>17.87</v>
       </c>
       <c r="L5" t="n">
         <v>59705.1</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>56.78</v>
+        <v>18.25</v>
       </c>
       <c r="L6" t="n">
         <v>52847.1</v>
@@ -22760,7 +22760,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>53.59</v>
+        <v>10.85</v>
       </c>
       <c r="L7" t="n">
         <v>56898</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17.66</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>26092.5</v>
@@ -22842,7 +22842,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>4738.5</v>
@@ -23682,7 +23682,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3359055.52</v>
+        <v>867889.9399999999</v>
       </c>
       <c r="L5" t="n">
         <v>10746918</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2757203.9</v>
+        <v>886244.11</v>
       </c>
       <c r="L6" t="n">
         <v>9512478</v>
@@ -23764,7 +23764,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2602213.15</v>
+        <v>526638.38</v>
       </c>
       <c r="L7" t="n">
         <v>10241640</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>857693.1800000001</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>4696650</v>
@@ -23846,7 +23846,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>852930</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Perfect.xlsx
@@ -560,7 +560,7 @@
         <v>553440</v>
       </c>
       <c r="H4" t="n">
-        <v>64260</v>
+        <v>70500</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>449</v>
       </c>
       <c r="L4" t="n">
-        <v>1465470</v>
+        <v>1547400</v>
       </c>
       <c r="M4" t="n">
-        <v>70530</v>
+        <v>46020</v>
       </c>
       <c r="N4" t="n">
-        <v>78630</v>
+        <v>74460</v>
       </c>
       <c r="O4" t="n">
-        <v>214560</v>
+        <v>218100</v>
       </c>
       <c r="P4" t="n">
-        <v>41760</v>
+        <v>15120</v>
       </c>
       <c r="Q4" t="n">
-        <v>219929.45</v>
+        <v>2279107.61</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>375360</v>
       </c>
       <c r="H5" t="n">
-        <v>54660</v>
+        <v>59010</v>
       </c>
       <c r="I5" t="n">
         <v>7</v>
@@ -625,22 +625,22 @@
         <v>267</v>
       </c>
       <c r="L5" t="n">
-        <v>919950</v>
+        <v>984150</v>
       </c>
       <c r="M5" t="n">
-        <v>51960</v>
+        <v>40410</v>
       </c>
       <c r="N5" t="n">
-        <v>80520</v>
+        <v>90870</v>
       </c>
       <c r="O5" t="n">
-        <v>187320</v>
+        <v>213450</v>
       </c>
       <c r="P5" t="n">
-        <v>50310</v>
+        <v>34290</v>
       </c>
       <c r="Q5" t="n">
-        <v>144394.66</v>
+        <v>1496347.93</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>237720</v>
       </c>
       <c r="H6" t="n">
-        <v>43050</v>
+        <v>46050</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>155</v>
       </c>
       <c r="L6" t="n">
-        <v>577740</v>
+        <v>575760</v>
       </c>
       <c r="M6" t="n">
-        <v>36120</v>
+        <v>23940</v>
       </c>
       <c r="N6" t="n">
-        <v>31920</v>
+        <v>44040</v>
       </c>
       <c r="O6" t="n">
-        <v>116850</v>
+        <v>125850</v>
       </c>
       <c r="P6" t="n">
-        <v>49560</v>
+        <v>36960</v>
       </c>
       <c r="Q6" t="n">
-        <v>96461.00999999999</v>
+        <v>999616.15</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>208770</v>
       </c>
       <c r="H7" t="n">
-        <v>47370</v>
+        <v>49440</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -731,22 +731,22 @@
         <v>176</v>
       </c>
       <c r="L7" t="n">
-        <v>541590</v>
+        <v>537960</v>
       </c>
       <c r="M7" t="n">
-        <v>25470</v>
+        <v>25200</v>
       </c>
       <c r="N7" t="n">
-        <v>11940</v>
+        <v>16440</v>
       </c>
       <c r="O7" t="n">
-        <v>86430</v>
+        <v>92100</v>
       </c>
       <c r="P7" t="n">
-        <v>60750</v>
+        <v>44220</v>
       </c>
       <c r="Q7" t="n">
-        <v>91307.21000000001</v>
+        <v>946207.8199999999</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>188130</v>
       </c>
       <c r="H8" t="n">
-        <v>30660</v>
+        <v>30060</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -784,22 +784,22 @@
         <v>108</v>
       </c>
       <c r="L8" t="n">
-        <v>468300</v>
+        <v>458400</v>
       </c>
       <c r="M8" t="n">
-        <v>21270</v>
+        <v>26280</v>
       </c>
       <c r="N8" t="n">
-        <v>2880</v>
+        <v>5580</v>
       </c>
       <c r="O8" t="n">
-        <v>60450</v>
+        <v>68580</v>
       </c>
       <c r="P8" t="n">
-        <v>66390</v>
+        <v>50640</v>
       </c>
       <c r="Q8" t="n">
-        <v>83664.50999999999</v>
+        <v>867007.23</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>154500</v>
       </c>
       <c r="H9" t="n">
-        <v>12180</v>
+        <v>15180</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -837,22 +837,22 @@
         <v>108</v>
       </c>
       <c r="L9" t="n">
-        <v>394590</v>
+        <v>411690</v>
       </c>
       <c r="M9" t="n">
-        <v>13110</v>
+        <v>34590</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9" t="n">
-        <v>57840</v>
+        <v>62700</v>
       </c>
       <c r="P9" t="n">
-        <v>67200</v>
+        <v>57990</v>
       </c>
       <c r="Q9" t="n">
-        <v>75505.10000000001</v>
+        <v>782452.05</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>160500</v>
       </c>
       <c r="H10" t="n">
-        <v>3780</v>
+        <v>4260</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -890,22 +890,22 @@
         <v>75</v>
       </c>
       <c r="L10" t="n">
-        <v>322320</v>
+        <v>346800</v>
       </c>
       <c r="M10" t="n">
-        <v>10560</v>
+        <v>24780</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>41310</v>
+        <v>55080</v>
       </c>
       <c r="P10" t="n">
-        <v>74730</v>
+        <v>72780</v>
       </c>
       <c r="Q10" t="n">
-        <v>68293.84</v>
+        <v>707722.49</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>84540</v>
       </c>
       <c r="H11" t="n">
-        <v>4230</v>
+        <v>4350</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -943,22 +943,22 @@
         <v>41</v>
       </c>
       <c r="L11" t="n">
-        <v>202320</v>
+        <v>241500</v>
       </c>
       <c r="M11" t="n">
-        <v>7140</v>
+        <v>25950</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>14640</v>
+        <v>26520</v>
       </c>
       <c r="P11" t="n">
-        <v>75030</v>
+        <v>88230</v>
       </c>
       <c r="Q11" t="n">
-        <v>43695.75</v>
+        <v>452814.85</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>62400</v>
       </c>
       <c r="H12" t="n">
-        <v>5670</v>
+        <v>5850</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -996,22 +996,22 @@
         <v>17</v>
       </c>
       <c r="L12" t="n">
-        <v>153780</v>
+        <v>197400</v>
       </c>
       <c r="M12" t="n">
-        <v>4530</v>
+        <v>23970</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5970</v>
+        <v>15300</v>
       </c>
       <c r="P12" t="n">
-        <v>64680</v>
+        <v>101160</v>
       </c>
       <c r="Q12" t="n">
-        <v>29398.34</v>
+        <v>304652.17</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>52710</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2970</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>8</v>
       </c>
       <c r="L13" t="n">
-        <v>119670</v>
+        <v>160980</v>
       </c>
       <c r="M13" t="n">
-        <v>2760</v>
+        <v>16440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>3960</v>
       </c>
       <c r="P13" t="n">
-        <v>44730</v>
+        <v>74850</v>
       </c>
       <c r="Q13" t="n">
-        <v>21139.27</v>
+        <v>219064.23</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>28890</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1102,22 +1102,22 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>48810</v>
+        <v>71820</v>
       </c>
       <c r="M14" t="n">
-        <v>1500</v>
+        <v>19800</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1800</v>
+        <v>2040</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>47610</v>
       </c>
       <c r="Q14" t="n">
-        <v>11160.89</v>
+        <v>115659.25</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>9390</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>23730</v>
+        <v>37230</v>
       </c>
       <c r="M15" t="n">
-        <v>360</v>
+        <v>6330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2940</v>
       </c>
       <c r="P15" t="n">
-        <v>27000</v>
+        <v>26580</v>
       </c>
       <c r="Q15" t="n">
-        <v>4003.98</v>
+        <v>41492.91</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>4200</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9630</v>
+        <v>26550</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>3660</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="P16" t="n">
-        <v>37470</v>
+        <v>47700</v>
       </c>
       <c r="Q16" t="n">
-        <v>2525.62</v>
+        <v>26172.75</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>1740</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3120</v>
+        <v>11370</v>
       </c>
       <c r="M17" t="n">
-        <v>180</v>
+        <v>2160</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>26250</v>
+        <v>43620</v>
       </c>
       <c r="Q17" t="n">
-        <v>1339.42</v>
+        <v>13880.31</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1470</v>
+        <v>7200</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>840</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>20940</v>
+        <v>29730</v>
       </c>
       <c r="Q18" t="n">
-        <v>634.33</v>
+        <v>6573.55</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
         <v>300</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1367,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1470</v>
+        <v>4290</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>18990</v>
+        <v>28710</v>
       </c>
       <c r="Q19" t="n">
-        <v>292.95</v>
+        <v>3035.81</v>
       </c>
     </row>
     <row r="20">
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3390</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6420</v>
+        <v>16350</v>
       </c>
       <c r="Q20" t="n">
-        <v>121.42</v>
+        <v>1258.27</v>
       </c>
     </row>
     <row r="21">
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.76</v>
+        <v>215.11</v>
       </c>
     </row>
     <row r="22">
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.46</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="23">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>8310</v>
       </c>
       <c r="H4" t="n">
-        <v>3450</v>
+        <v>3210</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>17010</v>
+        <v>17070</v>
       </c>
       <c r="M4" t="n">
-        <v>3240</v>
+        <v>1260</v>
       </c>
       <c r="N4" t="n">
-        <v>1050</v>
+        <v>300</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>108</v>
+        <v>12240</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>9030</v>
       </c>
       <c r="H5" t="n">
-        <v>4230</v>
+        <v>4920</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>20190</v>
+        <v>17520</v>
       </c>
       <c r="M5" t="n">
-        <v>6870</v>
+        <v>4710</v>
       </c>
       <c r="N5" t="n">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>203.8</v>
+        <v>23096.88</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8640</v>
       </c>
       <c r="H6" t="n">
-        <v>2700</v>
+        <v>3750</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,13 +1970,13 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>20070</v>
+        <v>17250</v>
       </c>
       <c r="M6" t="n">
-        <v>8910</v>
+        <v>4800</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O6" t="n">
         <v>30</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>507.84</v>
+        <v>57555.54</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>7500</v>
       </c>
       <c r="H7" t="n">
-        <v>2670</v>
+        <v>2430</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>9</v>
       </c>
       <c r="L7" t="n">
-        <v>24930</v>
+        <v>18750</v>
       </c>
       <c r="M7" t="n">
-        <v>8040</v>
+        <v>4380</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>780</v>
+        <v>390</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>884.95</v>
+        <v>100294.56</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>12600</v>
       </c>
       <c r="H8" t="n">
-        <v>4020</v>
+        <v>3480</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,22 +2076,22 @@
         <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>35730</v>
+        <v>28560</v>
       </c>
       <c r="M8" t="n">
-        <v>7380</v>
+        <v>2280</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>360</v>
+        <v>660</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1194.02</v>
+        <v>135322.38</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>18780</v>
       </c>
       <c r="H9" t="n">
-        <v>4170</v>
+        <v>5160</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>42090</v>
+        <v>38730</v>
       </c>
       <c r="M9" t="n">
-        <v>3960</v>
+        <v>2610</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1216.94</v>
+        <v>137920.32</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>20430</v>
       </c>
       <c r="H10" t="n">
-        <v>2880</v>
+        <v>2700</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -2182,22 +2182,22 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>45570</v>
+        <v>47520</v>
       </c>
       <c r="M10" t="n">
-        <v>3180</v>
+        <v>1170</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1303.67</v>
+        <v>147749.04</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>16710</v>
       </c>
       <c r="H11" t="n">
-        <v>3690</v>
+        <v>3570</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,22 +2235,22 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>49470</v>
+        <v>47820</v>
       </c>
       <c r="M11" t="n">
-        <v>2220</v>
+        <v>2550</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1181.09</v>
+        <v>133856.64</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>28050</v>
       </c>
       <c r="H12" t="n">
-        <v>5610</v>
+        <v>5370</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2288,22 +2288,22 @@
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>84090</v>
+        <v>80250</v>
       </c>
       <c r="M12" t="n">
-        <v>1560</v>
+        <v>4110</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1561.79</v>
+        <v>177002.64</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>31590</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2910</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>84690</v>
+        <v>96390</v>
       </c>
       <c r="M13" t="n">
-        <v>420</v>
+        <v>4200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1990.22</v>
+        <v>225558.72</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>20010</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>38310</v>
+        <v>46380</v>
       </c>
       <c r="M14" t="n">
-        <v>240</v>
+        <v>4050</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1253.5</v>
+        <v>142063.56</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>6780</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18450</v>
+        <v>24930</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3570</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>478.03</v>
+        <v>54177.3</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>3480</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8280</v>
+        <v>13440</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>348.79</v>
+        <v>39529.08</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2490</v>
+        <v>5970</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>1260</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>133.16</v>
+        <v>15091.92</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>870</v>
+        <v>1860</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>62.96</v>
+        <v>7135.92</v>
       </c>
     </row>
     <row r="19">
@@ -2647,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>1110</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.05</v>
+        <v>3292.56</v>
       </c>
     </row>
     <row r="20">
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3060</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2130</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.29</v>
+        <v>1165.86</v>
       </c>
     </row>
     <row r="21">
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2765,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.59</v>
+        <v>293.76</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.73</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="23">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1522.8</v>
+        <v>1771.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>0.99</v>
       </c>
       <c r="L5" t="n">
-        <v>4239.9</v>
+        <v>3679.2</v>
       </c>
       <c r="M5" t="n">
-        <v>137.4</v>
+        <v>94.2</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.19</v>
+        <v>1154.84</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>432</v>
       </c>
       <c r="H6" t="n">
-        <v>1539</v>
+        <v>2137.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>4.06</v>
       </c>
       <c r="L6" t="n">
-        <v>7425.9</v>
+        <v>6382.5</v>
       </c>
       <c r="M6" t="n">
-        <v>712.8</v>
+        <v>384</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>7.5</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>380.88</v>
+        <v>43166.66</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>1125</v>
       </c>
       <c r="H7" t="n">
-        <v>1949.1</v>
+        <v>1773.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>5.74</v>
       </c>
       <c r="L7" t="n">
-        <v>14958</v>
+        <v>11250</v>
       </c>
       <c r="M7" t="n">
-        <v>2814</v>
+        <v>1533</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>273</v>
+        <v>136.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>707.96</v>
+        <v>80235.64999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>8190</v>
       </c>
       <c r="H8" t="n">
-        <v>3417</v>
+        <v>2958</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>25368.3</v>
+        <v>20277.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4059</v>
+        <v>1254</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>162</v>
+        <v>297</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1134.32</v>
+        <v>128556.26</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>15963</v>
       </c>
       <c r="H9" t="n">
-        <v>4170</v>
+        <v>5160</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>34092.9</v>
+        <v>31371.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2772</v>
+        <v>1827</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>181.5</v>
+        <v>198</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1180.44</v>
+        <v>133782.71</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>20430</v>
       </c>
       <c r="H10" t="n">
-        <v>2880</v>
+        <v>2700</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -3474,22 +3474,22 @@
         <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>40557.3</v>
+        <v>42292.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2703</v>
+        <v>994.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>105</v>
+        <v>168</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1303.67</v>
+        <v>147749.04</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>16710</v>
       </c>
       <c r="H11" t="n">
-        <v>3690</v>
+        <v>3570</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,22 +3527,22 @@
         <v>2.7</v>
       </c>
       <c r="L11" t="n">
-        <v>49470</v>
+        <v>47820</v>
       </c>
       <c r="M11" t="n">
-        <v>1998</v>
+        <v>2295</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>51</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1181.09</v>
+        <v>133856.64</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>28050</v>
       </c>
       <c r="H12" t="n">
-        <v>5610</v>
+        <v>5370</v>
       </c>
       <c r="I12" t="n">
         <v>0.93</v>
@@ -3580,22 +3580,22 @@
         <v>4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>84090</v>
+        <v>80250</v>
       </c>
       <c r="M12" t="n">
-        <v>1482</v>
+        <v>3904.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1561.79</v>
+        <v>177002.64</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>31590</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2910</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>6.65</v>
       </c>
       <c r="L13" t="n">
-        <v>84690</v>
+        <v>96390</v>
       </c>
       <c r="M13" t="n">
-        <v>420</v>
+        <v>4200</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1990.22</v>
+        <v>225558.72</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>20010</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -3686,10 +3686,10 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>38310</v>
+        <v>46380</v>
       </c>
       <c r="M14" t="n">
-        <v>240</v>
+        <v>4050</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1253.5</v>
+        <v>142063.56</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>6780</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18450</v>
+        <v>24930</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>3570</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>478.04</v>
+        <v>54177.3</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>3480</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8280</v>
+        <v>13440</v>
       </c>
       <c r="M16" t="n">
-        <v>120</v>
+        <v>2100</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>348.79</v>
+        <v>39529.08</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2490</v>
+        <v>5970</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>1260</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>133.16</v>
+        <v>15091.92</v>
       </c>
     </row>
     <row r="18">
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>870</v>
+        <v>1860</v>
       </c>
       <c r="M18" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>62.96</v>
+        <v>7135.92</v>
       </c>
     </row>
     <row r="19">
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>1110</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.05</v>
+        <v>3292.56</v>
       </c>
     </row>
     <row r="20">
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3060</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2130</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.29</v>
+        <v>1165.86</v>
       </c>
     </row>
     <row r="21">
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.59</v>
+        <v>293.76</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.73</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="23">
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8679960</v>
+        <v>10095840</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>48216.11</v>
       </c>
       <c r="L5" t="n">
-        <v>763182</v>
+        <v>662256</v>
       </c>
       <c r="M5" t="n">
-        <v>48090</v>
+        <v>32970</v>
       </c>
       <c r="N5" t="n">
-        <v>408</v>
+        <v>1530</v>
       </c>
       <c r="O5" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6113.88</v>
+        <v>692906.4</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>23328</v>
       </c>
       <c r="H6" t="n">
-        <v>8772300</v>
+        <v>12183750</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>1336662</v>
+        <v>1148850</v>
       </c>
       <c r="M6" t="n">
-        <v>249480</v>
+        <v>134400</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="O6" t="n">
         <v>1275</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>228529.35</v>
+        <v>25899993</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>60750</v>
       </c>
       <c r="H7" t="n">
-        <v>11109870</v>
+        <v>10111230</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>278808.55</v>
       </c>
       <c r="L7" t="n">
-        <v>2692440</v>
+        <v>2025000</v>
       </c>
       <c r="M7" t="n">
-        <v>984900</v>
+        <v>536550</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>46410</v>
+        <v>23205</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>424776.96</v>
+        <v>48141388.8</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>442260</v>
       </c>
       <c r="H8" t="n">
-        <v>19476900</v>
+        <v>16860600</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,22 +4660,22 @@
         <v>321634.94</v>
       </c>
       <c r="L8" t="n">
-        <v>4566294</v>
+        <v>3649968</v>
       </c>
       <c r="M8" t="n">
-        <v>1420650</v>
+        <v>438900</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>27540</v>
+        <v>50490</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>680591.97</v>
+        <v>77133756.59999999</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>862002</v>
       </c>
       <c r="H9" t="n">
-        <v>23769000</v>
+        <v>29412000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>467885.62</v>
       </c>
       <c r="L9" t="n">
-        <v>6136722</v>
+        <v>5646834</v>
       </c>
       <c r="M9" t="n">
-        <v>970200</v>
+        <v>639450</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>30855</v>
+        <v>33660</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>708261.41</v>
+        <v>80269626.23999999</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1103220</v>
       </c>
       <c r="H10" t="n">
-        <v>16416000</v>
+        <v>15390000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -4766,22 +4766,22 @@
         <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>7300314</v>
+        <v>7612704</v>
       </c>
       <c r="M10" t="n">
-        <v>946050</v>
+        <v>348075</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17850</v>
+        <v>28560</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>782200.8</v>
+        <v>88649424</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>902340</v>
       </c>
       <c r="H11" t="n">
-        <v>21033000</v>
+        <v>20349000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,22 +4819,22 @@
         <v>130882.7</v>
       </c>
       <c r="L11" t="n">
-        <v>8904600</v>
+        <v>8607600</v>
       </c>
       <c r="M11" t="n">
-        <v>699300</v>
+        <v>803250</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8670</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>708652.8</v>
+        <v>80313984</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1514700</v>
       </c>
       <c r="H12" t="n">
-        <v>31977000</v>
+        <v>30609000</v>
       </c>
       <c r="I12" t="n">
         <v>180045.65</v>
@@ -4872,22 +4872,22 @@
         <v>225057.06</v>
       </c>
       <c r="L12" t="n">
-        <v>15136200</v>
+        <v>14445000</v>
       </c>
       <c r="M12" t="n">
-        <v>518700</v>
+        <v>1366575</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>40800</v>
+        <v>45900</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>937072.8</v>
+        <v>106201584</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1705860</v>
       </c>
       <c r="H13" t="n">
-        <v>12312000</v>
+        <v>16587000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>322727.45</v>
       </c>
       <c r="L13" t="n">
-        <v>15244200</v>
+        <v>17350200</v>
       </c>
       <c r="M13" t="n">
-        <v>147000</v>
+        <v>1470000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1194134.4</v>
+        <v>135335232</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>1080540</v>
       </c>
       <c r="H14" t="n">
-        <v>4275000</v>
+        <v>4788000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -4978,10 +4978,10 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>6895800</v>
+        <v>8348400</v>
       </c>
       <c r="M14" t="n">
-        <v>84000</v>
+        <v>1417500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>752101.2</v>
+        <v>85238136</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>366120</v>
       </c>
       <c r="H15" t="n">
-        <v>2907000</v>
+        <v>3933000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3321000</v>
+        <v>4487400</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>1249500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>286821</v>
+        <v>32506380</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>187920</v>
       </c>
       <c r="H16" t="n">
-        <v>1026000</v>
+        <v>1197000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1490400</v>
+        <v>2419200</v>
       </c>
       <c r="M16" t="n">
-        <v>42000</v>
+        <v>735000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>209271.6</v>
+        <v>23717448</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>48600</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>448200</v>
+        <v>1074600</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>441000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>79898.39999999999</v>
+        <v>9055152</v>
       </c>
     </row>
     <row r="18">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>156600</v>
+        <v>334800</v>
       </c>
       <c r="M18" t="n">
-        <v>63000</v>
+        <v>168000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>37778.4</v>
+        <v>4281552</v>
       </c>
     </row>
     <row r="19">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>113400</v>
+        <v>199800</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>294000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17431.2</v>
+        <v>1975536</v>
       </c>
     </row>
     <row r="20">
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>199800</v>
+        <v>550800</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>745500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>6172.2</v>
+        <v>699516</v>
       </c>
     </row>
     <row r="21">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1555.2</v>
+        <v>176256</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>437.4</v>
+        <v>49572</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>50640</v>
       </c>
       <c r="H4" t="n">
-        <v>9120</v>
+        <v>10290</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>153060</v>
+        <v>170970</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>11670</v>
+        <v>9570</v>
       </c>
       <c r="O4" t="n">
-        <v>20250</v>
+        <v>21540</v>
       </c>
       <c r="P4" t="n">
-        <v>12840</v>
+        <v>9120</v>
       </c>
       <c r="Q4" t="n">
-        <v>29128.14</v>
+        <v>153306</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>21570</v>
       </c>
       <c r="H5" t="n">
-        <v>5550</v>
+        <v>6510</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>62910</v>
+        <v>82950</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>14880</v>
+        <v>17100</v>
       </c>
       <c r="O5" t="n">
-        <v>10290</v>
+        <v>14610</v>
       </c>
       <c r="P5" t="n">
-        <v>10350</v>
+        <v>14280</v>
       </c>
       <c r="Q5" t="n">
-        <v>13457.22</v>
+        <v>70827.48</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>3150</v>
       </c>
       <c r="H6" t="n">
-        <v>480</v>
+        <v>1740</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12690</v>
+        <v>17940</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1650</v>
+        <v>3210</v>
       </c>
       <c r="O6" t="n">
-        <v>450</v>
+        <v>1710</v>
       </c>
       <c r="P6" t="n">
-        <v>6030</v>
+        <v>9480</v>
       </c>
       <c r="Q6" t="n">
-        <v>1666.22</v>
+        <v>8769.6</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>750</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3270</v>
+        <v>5370</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5850</v>
+        <v>8940</v>
       </c>
       <c r="Q7" t="n">
-        <v>134.2</v>
+        <v>706.3200000000001</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1830</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5040</v>
+        <v>9390</v>
       </c>
       <c r="Q8" t="n">
-        <v>54.17</v>
+        <v>285.12</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>210</v>
+        <v>1230</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4380</v>
+        <v>10320</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.24</v>
+        <v>132.84</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2220</v>
+        <v>5850</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.16</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1998</v>
+        <v>2343.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>5.96</v>
       </c>
       <c r="L5" t="n">
-        <v>13211.1</v>
+        <v>17419.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>148.8</v>
+        <v>171</v>
       </c>
       <c r="O5" t="n">
-        <v>514.5</v>
+        <v>730.5</v>
       </c>
       <c r="P5" t="n">
-        <v>207</v>
+        <v>285.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>672.86</v>
+        <v>3541.37</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>157.5</v>
       </c>
       <c r="H6" t="n">
-        <v>273.6</v>
+        <v>991.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4695.3</v>
+        <v>6637.8</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>82.5</v>
+        <v>160.5</v>
       </c>
       <c r="O6" t="n">
-        <v>112.5</v>
+        <v>427.5</v>
       </c>
       <c r="P6" t="n">
-        <v>904.5</v>
+        <v>1422</v>
       </c>
       <c r="Q6" t="n">
-        <v>1249.67</v>
+        <v>6577.2</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>112.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1962</v>
+        <v>3222</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1462.5</v>
+        <v>2235</v>
       </c>
       <c r="Q7" t="n">
-        <v>107.36</v>
+        <v>565.0599999999999</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>1299.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1915.2</v>
+        <v>3568.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>51.46</v>
+        <v>270.86</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>170.1</v>
+        <v>996.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2190</v>
+        <v>5160</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.48</v>
+        <v>128.85</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>213.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1887</v>
+        <v>4972.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.16</v>
+        <v>74.52</v>
       </c>
     </row>
     <row r="11">
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11388600</v>
+        <v>13358520</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>289296.65</v>
       </c>
       <c r="L5" t="n">
-        <v>2377998</v>
+        <v>3135510</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25296</v>
+        <v>29070</v>
       </c>
       <c r="O5" t="n">
-        <v>87465</v>
+        <v>124185</v>
       </c>
       <c r="P5" t="n">
-        <v>13455</v>
+        <v>18564</v>
       </c>
       <c r="Q5" t="n">
-        <v>403716.64</v>
+        <v>2124824.4</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>8505</v>
       </c>
       <c r="H6" t="n">
-        <v>1559520</v>
+        <v>5653260</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>845154</v>
+        <v>1194804</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>14025</v>
+        <v>27285</v>
       </c>
       <c r="O6" t="n">
-        <v>19125</v>
+        <v>72675</v>
       </c>
       <c r="P6" t="n">
-        <v>58792.5</v>
+        <v>92430</v>
       </c>
       <c r="Q6" t="n">
-        <v>749800.8</v>
+        <v>3946320</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>6075</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1248300</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>353160</v>
+        <v>579960</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>95062.5</v>
+        <v>145275</v>
       </c>
       <c r="Q7" t="n">
-        <v>64416.38</v>
+        <v>339033.6</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>233874</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>124488</v>
+        <v>231933</v>
       </c>
       <c r="Q8" t="n">
-        <v>30878.5</v>
+        <v>162518.4</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30618</v>
+        <v>179334</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>142350</v>
+        <v>335400</v>
       </c>
       <c r="Q9" t="n">
-        <v>14689.45</v>
+        <v>77312.88</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>38448</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>122655</v>
+        <v>323212.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8495.280000000001</v>
+        <v>44712</v>
       </c>
     </row>
     <row r="11">
@@ -8707,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1755</v>
+        <v>7020</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>91710</v>
       </c>
       <c r="H4" t="n">
-        <v>6210</v>
+        <v>7140</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>39</v>
       </c>
       <c r="L4" t="n">
-        <v>150270</v>
+        <v>169980</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>22380</v>
+        <v>23250</v>
       </c>
       <c r="O4" t="n">
-        <v>32760</v>
+        <v>33330</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35188.52</v>
+        <v>190945.44</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>28650</v>
       </c>
       <c r="H5" t="n">
-        <v>4020</v>
+        <v>4290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>54240</v>
+        <v>63690</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>9810</v>
+        <v>11970</v>
       </c>
       <c r="O5" t="n">
-        <v>29760</v>
+        <v>30180</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11263.79</v>
+        <v>61121.34</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>9540</v>
       </c>
       <c r="H6" t="n">
-        <v>1530</v>
+        <v>2160</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>16860</v>
+        <v>24120</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4890</v>
+        <v>5460</v>
       </c>
       <c r="O6" t="n">
-        <v>25140</v>
+        <v>25500</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2140.42</v>
+        <v>11614.68</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>3060</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4590</v>
+        <v>9210</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2400</v>
+        <v>3660</v>
       </c>
       <c r="O7" t="n">
-        <v>13650</v>
+        <v>17190</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>366.18</v>
+        <v>1987.02</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>960</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2520</v>
+        <v>4680</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>330</v>
+        <v>1440</v>
       </c>
       <c r="O8" t="n">
-        <v>3480</v>
+        <v>6360</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>138.16</v>
+        <v>749.7</v>
       </c>
     </row>
     <row r="9">
@@ -9881,22 +9881,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9" t="n">
-        <v>570</v>
+        <v>1110</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1447.2</v>
+        <v>1544.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>11390.4</v>
+        <v>13374.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>98.09999999999999</v>
+        <v>119.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1488</v>
+        <v>1509</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>563.1900000000001</v>
+        <v>3056.07</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>477</v>
       </c>
       <c r="H6" t="n">
-        <v>872.1</v>
+        <v>1231.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6238.2</v>
+        <v>8924.4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>244.5</v>
+        <v>273</v>
       </c>
       <c r="O6" t="n">
-        <v>6285</v>
+        <v>6375</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1605.31</v>
+        <v>8711.01</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>459</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2754</v>
+        <v>5526</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>168</v>
+        <v>256.2</v>
       </c>
       <c r="O7" t="n">
-        <v>4777.5</v>
+        <v>6016.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>292.94</v>
+        <v>1589.62</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>624</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1789.2</v>
+        <v>3322.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>66</v>
+        <v>288</v>
       </c>
       <c r="O8" t="n">
-        <v>1566</v>
+        <v>2862</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>131.25</v>
+        <v>712.21</v>
       </c>
     </row>
     <row r="9">
@@ -11173,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.3</v>
+        <v>194.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O9" t="n">
-        <v>313.5</v>
+        <v>610.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.26</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8249040</v>
+        <v>8803080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>208936.47</v>
       </c>
       <c r="L5" t="n">
-        <v>2050272</v>
+        <v>2407482</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>16677</v>
+        <v>20349</v>
       </c>
       <c r="O5" t="n">
-        <v>252960</v>
+        <v>256530</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>337913.69</v>
+        <v>1833640.2</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>25758</v>
       </c>
       <c r="H6" t="n">
-        <v>4970970</v>
+        <v>7017840</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1122876</v>
+        <v>1606392</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>41565</v>
+        <v>46410</v>
       </c>
       <c r="O6" t="n">
-        <v>1068450</v>
+        <v>1083750</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>963188.8199999999</v>
+        <v>5226606</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>24786</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>495720</v>
+        <v>994680</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>28560</v>
+        <v>43554</v>
       </c>
       <c r="O7" t="n">
-        <v>812175</v>
+        <v>1022805</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>175766.11</v>
+        <v>953769.6</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>33696</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>322056</v>
+        <v>598104</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>11220</v>
+        <v>48960</v>
       </c>
       <c r="O8" t="n">
-        <v>266220</v>
+        <v>486540</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>78750.63</v>
+        <v>427329</v>
       </c>
     </row>
     <row r="9">
@@ -12465,22 +12465,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4374</v>
+        <v>34992</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O9" t="n">
-        <v>53295</v>
+        <v>103785</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6757.02</v>
+        <v>36666</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>84000</v>
       </c>
       <c r="H4" t="n">
-        <v>7440</v>
+        <v>8100</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -13492,19 +13492,19 @@
         <v>132</v>
       </c>
       <c r="L4" t="n">
-        <v>178290</v>
+        <v>183120</v>
       </c>
       <c r="M4" t="n">
-        <v>10710</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>33030</v>
+        <v>36390</v>
       </c>
       <c r="P4" t="n">
-        <v>17040</v>
+        <v>2760</v>
       </c>
       <c r="Q4" t="n">
         <v>35219.73</v>
@@ -13533,7 +13533,7 @@
         <v>68460</v>
       </c>
       <c r="H5" t="n">
-        <v>5190</v>
+        <v>5760</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -13545,19 +13545,19 @@
         <v>95</v>
       </c>
       <c r="L5" t="n">
-        <v>151410</v>
+        <v>148530</v>
       </c>
       <c r="M5" t="n">
-        <v>17790</v>
+        <v>990</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31380</v>
+        <v>37350</v>
       </c>
       <c r="P5" t="n">
-        <v>25620</v>
+        <v>9390</v>
       </c>
       <c r="Q5" t="n">
         <v>30112.69</v>
@@ -13586,7 +13586,7 @@
         <v>62880</v>
       </c>
       <c r="H6" t="n">
-        <v>7560</v>
+        <v>7260</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>63</v>
       </c>
       <c r="L6" t="n">
-        <v>149340</v>
+        <v>128070</v>
       </c>
       <c r="M6" t="n">
-        <v>15000</v>
+        <v>1500</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22440</v>
+        <v>23970</v>
       </c>
       <c r="P6" t="n">
-        <v>29640</v>
+        <v>16260</v>
       </c>
       <c r="Q6" t="n">
         <v>27666.98</v>
@@ -13639,7 +13639,7 @@
         <v>83850</v>
       </c>
       <c r="H7" t="n">
-        <v>12270</v>
+        <v>12600</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>85</v>
       </c>
       <c r="L7" t="n">
-        <v>193710</v>
+        <v>174570</v>
       </c>
       <c r="M7" t="n">
-        <v>10230</v>
+        <v>4080</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>18150</v>
+        <v>16890</v>
       </c>
       <c r="P7" t="n">
-        <v>34020</v>
+        <v>22920</v>
       </c>
       <c r="Q7" t="n">
         <v>39284.76</v>
@@ -13692,7 +13692,7 @@
         <v>70110</v>
       </c>
       <c r="H8" t="n">
-        <v>4230</v>
+        <v>4590</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -13704,19 +13704,19 @@
         <v>48</v>
       </c>
       <c r="L8" t="n">
-        <v>155250</v>
+        <v>148170</v>
       </c>
       <c r="M8" t="n">
-        <v>7020</v>
+        <v>5760</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18720</v>
+        <v>19440</v>
       </c>
       <c r="P8" t="n">
-        <v>34170</v>
+        <v>28230</v>
       </c>
       <c r="Q8" t="n">
         <v>37490.46</v>
@@ -13745,7 +13745,7 @@
         <v>37170</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -13757,19 +13757,19 @@
         <v>35</v>
       </c>
       <c r="L9" t="n">
-        <v>88680</v>
+        <v>97110</v>
       </c>
       <c r="M9" t="n">
-        <v>4140</v>
+        <v>13350</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>24780</v>
+        <v>22680</v>
       </c>
       <c r="P9" t="n">
-        <v>32610</v>
+        <v>29610</v>
       </c>
       <c r="Q9" t="n">
         <v>30682.08</v>
@@ -13798,7 +13798,7 @@
         <v>30720</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13810,19 +13810,19 @@
         <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>46530</v>
+        <v>52380</v>
       </c>
       <c r="M10" t="n">
-        <v>2070</v>
+        <v>9810</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>17400</v>
+        <v>22800</v>
       </c>
       <c r="P10" t="n">
-        <v>35430</v>
+        <v>38670</v>
       </c>
       <c r="Q10" t="n">
         <v>21666.69</v>
@@ -13863,19 +13863,19 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>13050</v>
+        <v>25590</v>
       </c>
       <c r="M11" t="n">
-        <v>960</v>
+        <v>10140</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1860</v>
+        <v>3900</v>
       </c>
       <c r="P11" t="n">
-        <v>33840</v>
+        <v>37980</v>
       </c>
       <c r="Q11" t="n">
         <v>3563.05</v>
@@ -13904,7 +13904,7 @@
         <v>1440</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>34530</v>
       </c>
       <c r="M12" t="n">
-        <v>420</v>
+        <v>10740</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>32670</v>
+        <v>46500</v>
       </c>
       <c r="Q12" t="n">
         <v>531.77</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>21630</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>5070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24990</v>
+        <v>43110</v>
       </c>
       <c r="Q13" t="n">
         <v>228.11</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>9690</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>10080</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16590</v>
+        <v>31890</v>
       </c>
       <c r="Q14" t="n">
         <v>179.45</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>2880</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10710</v>
+        <v>9300</v>
       </c>
       <c r="Q15" t="n">
         <v>19.08</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>5730</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>690</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11610</v>
+        <v>18120</v>
       </c>
       <c r="Q16" t="n">
         <v>20.2</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>2760</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12480</v>
+        <v>25560</v>
       </c>
       <c r="Q17" t="n">
         <v>15.07</v>
@@ -14234,10 +14234,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>3780</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4560</v>
+        <v>12060</v>
       </c>
       <c r="Q18" t="n">
         <v>7.59</v>
@@ -14287,7 +14287,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1110</v>
+        <v>2640</v>
       </c>
       <c r="Q19" t="n">
         <v>2.9</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19677.6</v>
+        <v>21243.6</v>
       </c>
       <c r="I5" t="n">
         <v>2.32</v>
@@ -14837,22 +14837,22 @@
         <v>88.38</v>
       </c>
       <c r="L5" t="n">
-        <v>193189.5</v>
+        <v>206671.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1039.2</v>
+        <v>808.2</v>
       </c>
       <c r="N5" t="n">
-        <v>805.2</v>
+        <v>908.7</v>
       </c>
       <c r="O5" t="n">
-        <v>9366</v>
+        <v>10672.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1006.2</v>
+        <v>685.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>7219.73</v>
+        <v>74817.39999999999</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>11886</v>
       </c>
       <c r="H6" t="n">
-        <v>24538.5</v>
+        <v>26248.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>78.59</v>
       </c>
       <c r="L6" t="n">
-        <v>213763.8</v>
+        <v>213031.2</v>
       </c>
       <c r="M6" t="n">
-        <v>2889.6</v>
+        <v>1915.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1596</v>
+        <v>2202</v>
       </c>
       <c r="O6" t="n">
-        <v>29212.5</v>
+        <v>31462.5</v>
       </c>
       <c r="P6" t="n">
-        <v>7434</v>
+        <v>5544</v>
       </c>
       <c r="Q6" t="n">
-        <v>72345.75999999999</v>
+        <v>749712.11</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>31315.5</v>
       </c>
       <c r="H7" t="n">
-        <v>34580.1</v>
+        <v>36091.2</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -14943,22 +14943,22 @@
         <v>112.29</v>
       </c>
       <c r="L7" t="n">
-        <v>324954</v>
+        <v>322776</v>
       </c>
       <c r="M7" t="n">
-        <v>8914.5</v>
+        <v>8820</v>
       </c>
       <c r="N7" t="n">
-        <v>835.8</v>
+        <v>1150.8</v>
       </c>
       <c r="O7" t="n">
-        <v>30250.5</v>
+        <v>32235</v>
       </c>
       <c r="P7" t="n">
-        <v>15187.5</v>
+        <v>11055</v>
       </c>
       <c r="Q7" t="n">
-        <v>73045.77</v>
+        <v>756966.26</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>122284.5</v>
       </c>
       <c r="H8" t="n">
-        <v>26061</v>
+        <v>25551</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -14996,22 +14996,22 @@
         <v>79.48999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>332493</v>
+        <v>325464</v>
       </c>
       <c r="M8" t="n">
-        <v>11698.5</v>
+        <v>14454</v>
       </c>
       <c r="N8" t="n">
-        <v>576</v>
+        <v>1116</v>
       </c>
       <c r="O8" t="n">
-        <v>27202.5</v>
+        <v>30861</v>
       </c>
       <c r="P8" t="n">
-        <v>25228.2</v>
+        <v>19243.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>79481.28999999999</v>
+        <v>823656.87</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>131325</v>
       </c>
       <c r="H9" t="n">
-        <v>12180</v>
+        <v>15180</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -15049,22 +15049,22 @@
         <v>86.72</v>
       </c>
       <c r="L9" t="n">
-        <v>319617.9</v>
+        <v>333468.9</v>
       </c>
       <c r="M9" t="n">
-        <v>9177</v>
+        <v>24213</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O9" t="n">
-        <v>31812</v>
+        <v>34485</v>
       </c>
       <c r="P9" t="n">
-        <v>33600</v>
+        <v>28995</v>
       </c>
       <c r="Q9" t="n">
-        <v>73239.95</v>
+        <v>758978.49</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>160500</v>
       </c>
       <c r="H10" t="n">
-        <v>3780</v>
+        <v>4260</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -15102,22 +15102,22 @@
         <v>65.25</v>
       </c>
       <c r="L10" t="n">
-        <v>286864.8</v>
+        <v>308652</v>
       </c>
       <c r="M10" t="n">
-        <v>8976</v>
+        <v>21063</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>28917</v>
+        <v>38556</v>
       </c>
       <c r="P10" t="n">
-        <v>63520.5</v>
+        <v>61863</v>
       </c>
       <c r="Q10" t="n">
-        <v>68293.84</v>
+        <v>707722.49</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>84540</v>
       </c>
       <c r="H11" t="n">
-        <v>4230</v>
+        <v>4350</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -15155,22 +15155,22 @@
         <v>36.84</v>
       </c>
       <c r="L11" t="n">
-        <v>202320</v>
+        <v>241500</v>
       </c>
       <c r="M11" t="n">
-        <v>6426</v>
+        <v>23355</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12444</v>
+        <v>22542</v>
       </c>
       <c r="P11" t="n">
-        <v>67527</v>
+        <v>79407</v>
       </c>
       <c r="Q11" t="n">
-        <v>43695.75</v>
+        <v>452814.85</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>62400</v>
       </c>
       <c r="H12" t="n">
-        <v>5670</v>
+        <v>5850</v>
       </c>
       <c r="I12" t="n">
         <v>0.93</v>
@@ -15208,22 +15208,22 @@
         <v>15.76</v>
       </c>
       <c r="L12" t="n">
-        <v>153780</v>
+        <v>197400</v>
       </c>
       <c r="M12" t="n">
-        <v>4303.5</v>
+        <v>22771.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5970</v>
+        <v>15300</v>
       </c>
       <c r="P12" t="n">
-        <v>64680</v>
+        <v>101160</v>
       </c>
       <c r="Q12" t="n">
-        <v>29398.34</v>
+        <v>304652.17</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>52710</v>
       </c>
       <c r="H13" t="n">
-        <v>2160</v>
+        <v>2970</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>7.6</v>
       </c>
       <c r="L13" t="n">
-        <v>119670</v>
+        <v>160980</v>
       </c>
       <c r="M13" t="n">
-        <v>2760</v>
+        <v>16440</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>3960</v>
       </c>
       <c r="P13" t="n">
-        <v>44730</v>
+        <v>74850</v>
       </c>
       <c r="Q13" t="n">
-        <v>21139.27</v>
+        <v>219064.23</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>28890</v>
       </c>
       <c r="H14" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -15314,22 +15314,22 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>48810</v>
+        <v>71820</v>
       </c>
       <c r="M14" t="n">
-        <v>1500</v>
+        <v>19800</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1800</v>
+        <v>2040</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>47610</v>
       </c>
       <c r="Q14" t="n">
-        <v>11160.89</v>
+        <v>115659.25</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>9390</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>23730</v>
+        <v>37230</v>
       </c>
       <c r="M15" t="n">
-        <v>360</v>
+        <v>6330</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2940</v>
       </c>
       <c r="P15" t="n">
-        <v>27000</v>
+        <v>26580</v>
       </c>
       <c r="Q15" t="n">
-        <v>4003.98</v>
+        <v>41492.91</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>4200</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9630</v>
+        <v>26550</v>
       </c>
       <c r="M16" t="n">
-        <v>210</v>
+        <v>3660</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="P16" t="n">
-        <v>37470</v>
+        <v>47700</v>
       </c>
       <c r="Q16" t="n">
-        <v>2525.62</v>
+        <v>26172.75</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>1740</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,10 +15473,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3120</v>
+        <v>11370</v>
       </c>
       <c r="M17" t="n">
-        <v>180</v>
+        <v>2160</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -15485,10 +15485,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>26250</v>
+        <v>43620</v>
       </c>
       <c r="Q17" t="n">
-        <v>1339.42</v>
+        <v>13880.31</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1470</v>
+        <v>7200</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>840</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>20940</v>
+        <v>29730</v>
       </c>
       <c r="Q18" t="n">
-        <v>634.33</v>
+        <v>6573.55</v>
       </c>
     </row>
     <row r="19">
@@ -15567,7 +15567,7 @@
         <v>300</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15579,22 +15579,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1470</v>
+        <v>4290</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>930</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>18990</v>
+        <v>28710</v>
       </c>
       <c r="Q19" t="n">
-        <v>292.95</v>
+        <v>3035.81</v>
       </c>
     </row>
     <row r="20">
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3390</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6420</v>
+        <v>16350</v>
       </c>
       <c r="Q20" t="n">
-        <v>121.42</v>
+        <v>1258.27</v>
       </c>
     </row>
     <row r="21">
@@ -15673,7 +15673,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -15685,10 +15685,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1140</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15697,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.76</v>
+        <v>215.11</v>
       </c>
     </row>
     <row r="22">
@@ -15738,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.46</v>
+        <v>35.85</v>
       </c>
     </row>
     <row r="23">
@@ -15791,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1868.4</v>
+        <v>2073.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
@@ -16129,19 +16129,19 @@
         <v>31.44</v>
       </c>
       <c r="L5" t="n">
-        <v>31796.1</v>
+        <v>31191.3</v>
       </c>
       <c r="M5" t="n">
-        <v>355.8</v>
+        <v>19.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1569</v>
+        <v>1867.5</v>
       </c>
       <c r="P5" t="n">
-        <v>512.4</v>
+        <v>187.8</v>
       </c>
       <c r="Q5" t="n">
         <v>1505.63</v>
@@ -16170,7 +16170,7 @@
         <v>3144</v>
       </c>
       <c r="H6" t="n">
-        <v>4309.2</v>
+        <v>4138.2</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>31.94</v>
       </c>
       <c r="L6" t="n">
-        <v>55255.8</v>
+        <v>47385.9</v>
       </c>
       <c r="M6" t="n">
-        <v>1200</v>
+        <v>120</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5610</v>
+        <v>5992.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4446</v>
+        <v>2439</v>
       </c>
       <c r="Q6" t="n">
         <v>20750.23</v>
@@ -16223,7 +16223,7 @@
         <v>12577.5</v>
       </c>
       <c r="H7" t="n">
-        <v>8957.1</v>
+        <v>9198</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>54.23</v>
       </c>
       <c r="L7" t="n">
-        <v>116226</v>
+        <v>104742</v>
       </c>
       <c r="M7" t="n">
-        <v>3580.5</v>
+        <v>1428</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6352.5</v>
+        <v>5911.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8505</v>
+        <v>5730</v>
       </c>
       <c r="Q7" t="n">
         <v>31427.81</v>
@@ -16276,7 +16276,7 @@
         <v>45571.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3595.5</v>
+        <v>3901.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -16288,19 +16288,19 @@
         <v>35.33</v>
       </c>
       <c r="L8" t="n">
-        <v>110227.5</v>
+        <v>105200.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3861</v>
+        <v>3168</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8424</v>
+        <v>8748</v>
       </c>
       <c r="P8" t="n">
-        <v>12984.6</v>
+        <v>10727.4</v>
       </c>
       <c r="Q8" t="n">
         <v>35615.93</v>
@@ -16329,7 +16329,7 @@
         <v>31594.5</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -16341,19 +16341,19 @@
         <v>28.1</v>
       </c>
       <c r="L9" t="n">
-        <v>71830.8</v>
+        <v>78659.10000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>2898</v>
+        <v>9345</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>13629</v>
+        <v>12474</v>
       </c>
       <c r="P9" t="n">
-        <v>16305</v>
+        <v>14805</v>
       </c>
       <c r="Q9" t="n">
         <v>29761.61</v>
@@ -16382,7 +16382,7 @@
         <v>30720</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16394,19 +16394,19 @@
         <v>12.18</v>
       </c>
       <c r="L10" t="n">
-        <v>41411.7</v>
+        <v>46618.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1759.5</v>
+        <v>8338.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12180</v>
+        <v>15960</v>
       </c>
       <c r="P10" t="n">
-        <v>30115.5</v>
+        <v>32869.5</v>
       </c>
       <c r="Q10" t="n">
         <v>21666.69</v>
@@ -16447,19 +16447,19 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>13050</v>
+        <v>25590</v>
       </c>
       <c r="M11" t="n">
-        <v>864</v>
+        <v>9126</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1581</v>
+        <v>3315</v>
       </c>
       <c r="P11" t="n">
-        <v>30456</v>
+        <v>34182</v>
       </c>
       <c r="Q11" t="n">
         <v>3563.05</v>
@@ -16488,7 +16488,7 @@
         <v>1440</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>2.78</v>
       </c>
       <c r="L12" t="n">
-        <v>6030</v>
+        <v>34530</v>
       </c>
       <c r="M12" t="n">
-        <v>399</v>
+        <v>10203</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P12" t="n">
-        <v>32670</v>
+        <v>46500</v>
       </c>
       <c r="Q12" t="n">
         <v>531.77</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3120</v>
+        <v>21630</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>5070</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24990</v>
+        <v>43110</v>
       </c>
       <c r="Q13" t="n">
         <v>228.11</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>9690</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>10080</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16590</v>
+        <v>31890</v>
       </c>
       <c r="Q14" t="n">
         <v>179.45</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>510</v>
+        <v>2880</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>1020</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10710</v>
+        <v>9300</v>
       </c>
       <c r="Q15" t="n">
         <v>19.08</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>300</v>
+        <v>5730</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>690</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11610</v>
+        <v>18120</v>
       </c>
       <c r="Q16" t="n">
         <v>20.2</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>270</v>
+        <v>2760</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12480</v>
+        <v>25560</v>
       </c>
       <c r="Q17" t="n">
         <v>15.07</v>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>510</v>
+        <v>3780</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4560</v>
+        <v>12060</v>
       </c>
       <c r="Q18" t="n">
         <v>7.59</v>
@@ -16871,7 +16871,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>600</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1110</v>
+        <v>2640</v>
       </c>
       <c r="Q19" t="n">
         <v>2.9</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10649880</v>
+        <v>11819520</v>
       </c>
       <c r="I5" t="n">
         <v>321440.72</v>
@@ -17421,19 +17421,19 @@
         <v>1526843.42</v>
       </c>
       <c r="L5" t="n">
-        <v>5723298</v>
+        <v>5614434</v>
       </c>
       <c r="M5" t="n">
-        <v>124530</v>
+        <v>6930</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>266730</v>
+        <v>317475</v>
       </c>
       <c r="P5" t="n">
-        <v>33306</v>
+        <v>12207</v>
       </c>
       <c r="Q5" t="n">
         <v>903380.8</v>
@@ -17462,7 +17462,7 @@
         <v>169776</v>
       </c>
       <c r="H6" t="n">
-        <v>24562440</v>
+        <v>23587740</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>1550927.2</v>
       </c>
       <c r="L6" t="n">
-        <v>9946044</v>
+        <v>8529462</v>
       </c>
       <c r="M6" t="n">
-        <v>420000</v>
+        <v>42000</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>953700</v>
+        <v>1018725</v>
       </c>
       <c r="P6" t="n">
-        <v>288990</v>
+        <v>158535</v>
       </c>
       <c r="Q6" t="n">
         <v>12450140.64</v>
@@ -17515,7 +17515,7 @@
         <v>679185</v>
       </c>
       <c r="H7" t="n">
-        <v>51055470</v>
+        <v>52428600</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>2633191.88</v>
       </c>
       <c r="L7" t="n">
-        <v>20920680</v>
+        <v>18853560</v>
       </c>
       <c r="M7" t="n">
-        <v>1253175</v>
+        <v>499800</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1079925</v>
+        <v>1004955</v>
       </c>
       <c r="P7" t="n">
-        <v>552825</v>
+        <v>372450</v>
       </c>
       <c r="Q7" t="n">
         <v>18856685.95</v>
@@ -17568,7 +17568,7 @@
         <v>2460861</v>
       </c>
       <c r="H8" t="n">
-        <v>20494350</v>
+        <v>22238550</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -17580,19 +17580,19 @@
         <v>1715386.37</v>
       </c>
       <c r="L8" t="n">
-        <v>19840950</v>
+        <v>18936126</v>
       </c>
       <c r="M8" t="n">
-        <v>1351350</v>
+        <v>1108800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1432080</v>
+        <v>1487160</v>
       </c>
       <c r="P8" t="n">
-        <v>843999</v>
+        <v>697281</v>
       </c>
       <c r="Q8" t="n">
         <v>21369560.83</v>
@@ -17621,7 +17621,7 @@
         <v>1706103</v>
       </c>
       <c r="H9" t="n">
-        <v>2907000</v>
+        <v>4104000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -17633,19 +17633,19 @@
         <v>1364666.38</v>
       </c>
       <c r="L9" t="n">
-        <v>12929544</v>
+        <v>14158638</v>
       </c>
       <c r="M9" t="n">
-        <v>1014300</v>
+        <v>3270750</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2316930</v>
+        <v>2120580</v>
       </c>
       <c r="P9" t="n">
-        <v>1059825</v>
+        <v>962325</v>
       </c>
       <c r="Q9" t="n">
         <v>17856968.46</v>
@@ -17674,7 +17674,7 @@
         <v>1658880</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -17686,19 +17686,19 @@
         <v>591412.08</v>
       </c>
       <c r="L10" t="n">
-        <v>7454106</v>
+        <v>8391276</v>
       </c>
       <c r="M10" t="n">
-        <v>615825</v>
+        <v>2918475</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2070600</v>
+        <v>2713200</v>
       </c>
       <c r="P10" t="n">
-        <v>1957507.5</v>
+        <v>2136517.5</v>
       </c>
       <c r="Q10" t="n">
         <v>13000016.16</v>
@@ -17739,19 +17739,19 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>2349000</v>
+        <v>4606200</v>
       </c>
       <c r="M11" t="n">
-        <v>302400</v>
+        <v>3194100</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>268770</v>
+        <v>563550</v>
       </c>
       <c r="P11" t="n">
-        <v>1979640</v>
+        <v>2221830</v>
       </c>
       <c r="Q11" t="n">
         <v>2137831.92</v>
@@ -17780,7 +17780,7 @@
         <v>77760</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>135034.24</v>
       </c>
       <c r="L12" t="n">
-        <v>1085400</v>
+        <v>6215400</v>
       </c>
       <c r="M12" t="n">
-        <v>139650</v>
+        <v>3571050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P12" t="n">
-        <v>2123550</v>
+        <v>3022500</v>
       </c>
       <c r="Q12" t="n">
         <v>319064.4</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>561600</v>
+        <v>3893400</v>
       </c>
       <c r="M13" t="n">
-        <v>63000</v>
+        <v>1774500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1624350</v>
+        <v>2802150</v>
       </c>
       <c r="Q13" t="n">
         <v>136866.24</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>232200</v>
+        <v>1744200</v>
       </c>
       <c r="M14" t="n">
-        <v>42000</v>
+        <v>3528000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1078350</v>
+        <v>2072850</v>
       </c>
       <c r="Q14" t="n">
         <v>107671.68</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>91800</v>
+        <v>518400</v>
       </c>
       <c r="M15" t="n">
-        <v>21000</v>
+        <v>357000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>696150</v>
+        <v>604500</v>
       </c>
       <c r="Q15" t="n">
         <v>11450.16</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>54000</v>
+        <v>1031400</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>241500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>754650</v>
+        <v>1177800</v>
       </c>
       <c r="Q16" t="n">
         <v>12119.76</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>48600</v>
+        <v>496800</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>52500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>811200</v>
+        <v>1661400</v>
       </c>
       <c r="Q17" t="n">
         <v>9039.6</v>
@@ -18110,10 +18110,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>91800</v>
+        <v>680400</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>296400</v>
+        <v>783900</v>
       </c>
       <c r="Q18" t="n">
         <v>4553.28</v>
@@ -18163,7 +18163,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>108000</v>
+        <v>286200</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>72150</v>
+        <v>171600</v>
       </c>
       <c r="Q19" t="n">
         <v>1740.96</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>37800</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>117300</v>
       </c>
       <c r="H4" t="n">
-        <v>14850</v>
+        <v>16440</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>374580</v>
+        <v>414210</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>16290</v>
+        <v>13410</v>
       </c>
       <c r="O4" t="n">
-        <v>54600</v>
+        <v>52860</v>
       </c>
       <c r="P4" t="n">
-        <v>7680</v>
+        <v>2520</v>
       </c>
       <c r="Q4" t="n">
-        <v>37000.37</v>
+        <v>423962.55</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>35280</v>
       </c>
       <c r="H5" t="n">
-        <v>3180</v>
+        <v>5730</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>125790</v>
+        <v>156480</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25950</v>
+        <v>29310</v>
       </c>
       <c r="O5" t="n">
-        <v>36750</v>
+        <v>50340</v>
       </c>
       <c r="P5" t="n">
-        <v>6510</v>
+        <v>8340</v>
       </c>
       <c r="Q5" t="n">
-        <v>13036.2</v>
+        <v>149373.18</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>4980</v>
       </c>
       <c r="H6" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>21270</v>
+        <v>32670</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7230</v>
+        <v>12360</v>
       </c>
       <c r="O6" t="n">
-        <v>7590</v>
+        <v>10380</v>
       </c>
       <c r="P6" t="n">
-        <v>4140</v>
+        <v>7950</v>
       </c>
       <c r="Q6" t="n">
-        <v>1293.49</v>
+        <v>14821.29</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3720</v>
+        <v>9030</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="O7" t="n">
-        <v>2520</v>
+        <v>3450</v>
       </c>
       <c r="P7" t="n">
-        <v>3600</v>
+        <v>8880</v>
       </c>
       <c r="Q7" t="n">
-        <v>166.67</v>
+        <v>1909.71</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>720</v>
+        <v>1860</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18881,13 +18881,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>720</v>
+        <v>1410</v>
       </c>
       <c r="P8" t="n">
-        <v>1980</v>
+        <v>6450</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.95</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1144.8</v>
+        <v>2062.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>5.63</v>
       </c>
       <c r="L5" t="n">
-        <v>26415.9</v>
+        <v>32860.8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>259.5</v>
+        <v>293.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1837.5</v>
+        <v>2517</v>
       </c>
       <c r="P5" t="n">
-        <v>130.2</v>
+        <v>166.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>651.8099999999999</v>
+        <v>7468.66</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>249</v>
       </c>
       <c r="H6" t="n">
-        <v>222.3</v>
+        <v>307.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7869.9</v>
+        <v>12087.9</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>361.5</v>
+        <v>618</v>
       </c>
       <c r="O6" t="n">
-        <v>1897.5</v>
+        <v>2595</v>
       </c>
       <c r="P6" t="n">
-        <v>621</v>
+        <v>1192.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>970.12</v>
+        <v>11115.97</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2232</v>
+        <v>5418</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14.7</v>
+        <v>35.7</v>
       </c>
       <c r="O7" t="n">
-        <v>882</v>
+        <v>1207.5</v>
       </c>
       <c r="P7" t="n">
-        <v>900</v>
+        <v>2220</v>
       </c>
       <c r="Q7" t="n">
-        <v>133.33</v>
+        <v>1527.77</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>511.2</v>
+        <v>1320.6</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20173,13 +20173,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>324</v>
+        <v>634.5</v>
       </c>
       <c r="P8" t="n">
-        <v>752.4</v>
+        <v>2451</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.2</v>
+        <v>162.71</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>133.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6525360</v>
+        <v>11757960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>273224.61</v>
       </c>
       <c r="L5" t="n">
-        <v>4754862</v>
+        <v>5914944</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>44115</v>
+        <v>49827</v>
       </c>
       <c r="O5" t="n">
-        <v>312375</v>
+        <v>427890</v>
       </c>
       <c r="P5" t="n">
-        <v>8463</v>
+        <v>10842</v>
       </c>
       <c r="Q5" t="n">
-        <v>391086.14</v>
+        <v>4481195.4</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>13446</v>
       </c>
       <c r="H6" t="n">
-        <v>1267110</v>
+        <v>1754460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1416582</v>
+        <v>2175822</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>61455</v>
+        <v>105060</v>
       </c>
       <c r="O6" t="n">
-        <v>322575</v>
+        <v>441150</v>
       </c>
       <c r="P6" t="n">
-        <v>40365</v>
+        <v>77512.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>582072.48</v>
+        <v>6669580.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>401760</v>
+        <v>975240</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2499</v>
+        <v>6069</v>
       </c>
       <c r="O7" t="n">
-        <v>149940</v>
+        <v>205275</v>
       </c>
       <c r="P7" t="n">
-        <v>58500</v>
+        <v>144300</v>
       </c>
       <c r="Q7" t="n">
-        <v>79999.49000000001</v>
+        <v>916660.8</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>92016</v>
+        <v>237708</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21465,13 +21465,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>55080</v>
+        <v>107865</v>
       </c>
       <c r="P8" t="n">
-        <v>48906</v>
+        <v>159315</v>
       </c>
       <c r="Q8" t="n">
-        <v>8519.9</v>
+        <v>97623.89999999999</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>24030</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>112162320</v>
+        <v>121088520</v>
       </c>
       <c r="I5" t="n">
         <v>450017.01</v>
@@ -22589,22 +22589,22 @@
         <v>4291233.61</v>
       </c>
       <c r="L5" t="n">
-        <v>34774110</v>
+        <v>37200870</v>
       </c>
       <c r="M5" t="n">
-        <v>363720</v>
+        <v>282870</v>
       </c>
       <c r="N5" t="n">
-        <v>136884</v>
+        <v>154479</v>
       </c>
       <c r="O5" t="n">
-        <v>1592220</v>
+        <v>1814325</v>
       </c>
       <c r="P5" t="n">
-        <v>65403</v>
+        <v>44577</v>
       </c>
       <c r="Q5" t="n">
-        <v>4331839.93</v>
+        <v>44890438.01</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>641844</v>
       </c>
       <c r="H6" t="n">
-        <v>139869450</v>
+        <v>149616450</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>3815773.26</v>
       </c>
       <c r="L6" t="n">
-        <v>38477484</v>
+        <v>38345616</v>
       </c>
       <c r="M6" t="n">
-        <v>1011360</v>
+        <v>670320</v>
       </c>
       <c r="N6" t="n">
-        <v>271320</v>
+        <v>374340</v>
       </c>
       <c r="O6" t="n">
-        <v>4966125</v>
+        <v>5348625</v>
       </c>
       <c r="P6" t="n">
-        <v>483210</v>
+        <v>360360</v>
       </c>
       <c r="Q6" t="n">
-        <v>43407456.12</v>
+        <v>449827267.05</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1691037</v>
       </c>
       <c r="H7" t="n">
-        <v>197106570</v>
+        <v>205719840</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -22695,22 +22695,22 @@
         <v>5452256.13</v>
       </c>
       <c r="L7" t="n">
-        <v>58491720</v>
+        <v>58099680</v>
       </c>
       <c r="M7" t="n">
-        <v>3120075</v>
+        <v>3087000</v>
       </c>
       <c r="N7" t="n">
-        <v>142086</v>
+        <v>195636</v>
       </c>
       <c r="O7" t="n">
-        <v>5142585</v>
+        <v>5479950</v>
       </c>
       <c r="P7" t="n">
-        <v>987187.5</v>
+        <v>718575</v>
       </c>
       <c r="Q7" t="n">
-        <v>43827462.72</v>
+        <v>454179754.8</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>6603363</v>
       </c>
       <c r="H8" t="n">
-        <v>148547700</v>
+        <v>145640700</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -22748,22 +22748,22 @@
         <v>3859619.33</v>
       </c>
       <c r="L8" t="n">
-        <v>59848740</v>
+        <v>58583520</v>
       </c>
       <c r="M8" t="n">
-        <v>4094475</v>
+        <v>5058900</v>
       </c>
       <c r="N8" t="n">
-        <v>97920</v>
+        <v>189720</v>
       </c>
       <c r="O8" t="n">
-        <v>4624425</v>
+        <v>5246370</v>
       </c>
       <c r="P8" t="n">
-        <v>1639833</v>
+        <v>1250808</v>
       </c>
       <c r="Q8" t="n">
-        <v>47688771.38</v>
+        <v>494194122.81</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7091550</v>
       </c>
       <c r="H9" t="n">
-        <v>69426000</v>
+        <v>86526000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -22801,22 +22801,22 @@
         <v>4210970.54</v>
       </c>
       <c r="L9" t="n">
-        <v>57531222</v>
+        <v>60024402</v>
       </c>
       <c r="M9" t="n">
-        <v>3211950</v>
+        <v>8474550</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O9" t="n">
-        <v>5408040</v>
+        <v>5862450</v>
       </c>
       <c r="P9" t="n">
-        <v>2184000</v>
+        <v>1884675</v>
       </c>
       <c r="Q9" t="n">
-        <v>43943968.43</v>
+        <v>455387092.23</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>8667000</v>
       </c>
       <c r="H10" t="n">
-        <v>21546000</v>
+        <v>24282000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -22854,22 +22854,22 @@
         <v>3168279</v>
       </c>
       <c r="L10" t="n">
-        <v>51635664</v>
+        <v>55557360</v>
       </c>
       <c r="M10" t="n">
-        <v>3141600</v>
+        <v>7372050</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>4915890</v>
+        <v>6554520</v>
       </c>
       <c r="P10" t="n">
-        <v>4128832.5</v>
+        <v>4021095</v>
       </c>
       <c r="Q10" t="n">
-        <v>40976305.92</v>
+        <v>424633492.8</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>4565160</v>
       </c>
       <c r="H11" t="n">
-        <v>24111000</v>
+        <v>24795000</v>
       </c>
       <c r="I11" t="n">
         <v>349020.53</v>
@@ -22907,22 +22907,22 @@
         <v>1788730.21</v>
       </c>
       <c r="L11" t="n">
-        <v>36417600</v>
+        <v>43470000</v>
       </c>
       <c r="M11" t="n">
-        <v>2249100</v>
+        <v>8174250</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2115480</v>
+        <v>3832140</v>
       </c>
       <c r="P11" t="n">
-        <v>4389255</v>
+        <v>5161455</v>
       </c>
       <c r="Q11" t="n">
-        <v>26217451.44</v>
+        <v>271688912.1</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>3369600</v>
       </c>
       <c r="H12" t="n">
-        <v>32319000</v>
+        <v>33345000</v>
       </c>
       <c r="I12" t="n">
         <v>180045.65</v>
@@ -22960,22 +22960,22 @@
         <v>765194</v>
       </c>
       <c r="L12" t="n">
-        <v>27680400</v>
+        <v>35532000</v>
       </c>
       <c r="M12" t="n">
-        <v>1506225</v>
+        <v>7970025</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1014900</v>
+        <v>2601000</v>
       </c>
       <c r="P12" t="n">
-        <v>4204200</v>
+        <v>6575400</v>
       </c>
       <c r="Q12" t="n">
-        <v>17639004.96</v>
+        <v>182791301.4</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>2846340</v>
       </c>
       <c r="H13" t="n">
-        <v>12312000</v>
+        <v>16929000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>368831.38</v>
       </c>
       <c r="L13" t="n">
-        <v>21540600</v>
+        <v>28976400</v>
       </c>
       <c r="M13" t="n">
-        <v>966000</v>
+        <v>5754000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>418200</v>
+        <v>673200</v>
       </c>
       <c r="P13" t="n">
-        <v>2907450</v>
+        <v>4865250</v>
       </c>
       <c r="Q13" t="n">
-        <v>12683563.2</v>
+        <v>131438538</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>1560060</v>
       </c>
       <c r="H14" t="n">
-        <v>4275000</v>
+        <v>4788000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -23066,22 +23066,22 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>8785800</v>
+        <v>12927600</v>
       </c>
       <c r="M14" t="n">
-        <v>525000</v>
+        <v>6930000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>306000</v>
+        <v>346800</v>
       </c>
       <c r="P14" t="n">
-        <v>2047500</v>
+        <v>3094650</v>
       </c>
       <c r="Q14" t="n">
-        <v>6696535.68</v>
+        <v>69395551.2</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>507060</v>
       </c>
       <c r="H15" t="n">
-        <v>2907000</v>
+        <v>3933000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4271400</v>
+        <v>6701400</v>
       </c>
       <c r="M15" t="n">
-        <v>126000</v>
+        <v>2215500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>459000</v>
+        <v>499800</v>
       </c>
       <c r="P15" t="n">
-        <v>1755000</v>
+        <v>1727700</v>
       </c>
       <c r="Q15" t="n">
-        <v>2402390.88</v>
+        <v>24895744.2</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>226800</v>
       </c>
       <c r="H16" t="n">
-        <v>1026000</v>
+        <v>1197000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1733400</v>
+        <v>4779000</v>
       </c>
       <c r="M16" t="n">
-        <v>73500</v>
+        <v>1281000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>15300</v>
+        <v>81600</v>
       </c>
       <c r="P16" t="n">
-        <v>2435550</v>
+        <v>3100500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1515371.76</v>
+        <v>15703650.9</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>93960</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>561600</v>
+        <v>2046600</v>
       </c>
       <c r="M17" t="n">
-        <v>63000</v>
+        <v>756000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1706250</v>
+        <v>2835300</v>
       </c>
       <c r="Q17" t="n">
-        <v>803653.92</v>
+        <v>8328187.8</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>264600</v>
+        <v>1296000</v>
       </c>
       <c r="M18" t="n">
-        <v>73500</v>
+        <v>294000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1361100</v>
+        <v>1932450</v>
       </c>
       <c r="Q18" t="n">
-        <v>380600.64</v>
+        <v>3944127.6</v>
       </c>
     </row>
     <row r="19">
@@ -23319,7 +23319,7 @@
         <v>16200</v>
       </c>
       <c r="H19" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23331,22 +23331,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>264600</v>
+        <v>772200</v>
       </c>
       <c r="M19" t="n">
-        <v>42000</v>
+        <v>325500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P19" t="n">
-        <v>1234350</v>
+        <v>1866150</v>
       </c>
       <c r="Q19" t="n">
-        <v>175770</v>
+        <v>1821487.5</v>
       </c>
     </row>
     <row r="20">
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>199800</v>
+        <v>610200</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>777000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>417300</v>
+        <v>1062750</v>
       </c>
       <c r="Q20" t="n">
-        <v>72852.48</v>
+        <v>754963.2</v>
       </c>
     </row>
     <row r="21">
@@ -23425,7 +23425,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -23437,10 +23437,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>205200</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23449,10 +23449,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q21" t="n">
-        <v>12454.56</v>
+        <v>129065.4</v>
       </c>
     </row>
     <row r="22">
@@ -23490,7 +23490,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2075.76</v>
+        <v>21510.9</v>
       </c>
     </row>
     <row r="23">
@@ -23543,7 +23543,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -23816,7 +23816,7 @@
         <v>45870</v>
       </c>
       <c r="H4" t="n">
-        <v>2850</v>
+        <v>2340</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>72</v>
       </c>
       <c r="L4" t="n">
-        <v>131430</v>
+        <v>112320</v>
       </c>
       <c r="M4" t="n">
-        <v>45600</v>
+        <v>42630</v>
       </c>
       <c r="N4" t="n">
-        <v>11040</v>
+        <v>9240</v>
       </c>
       <c r="O4" t="n">
-        <v>16140</v>
+        <v>19380</v>
       </c>
       <c r="P4" t="n">
-        <v>1710</v>
+        <v>390</v>
       </c>
       <c r="Q4" t="n">
-        <v>9505.25</v>
+        <v>93188.7</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>61680</v>
       </c>
       <c r="H5" t="n">
-        <v>6600</v>
+        <v>5370</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -23881,22 +23881,22 @@
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>163200</v>
+        <v>148290</v>
       </c>
       <c r="M5" t="n">
-        <v>19920</v>
+        <v>31110</v>
       </c>
       <c r="N5" t="n">
-        <v>20850</v>
+        <v>20280</v>
       </c>
       <c r="O5" t="n">
-        <v>19650</v>
+        <v>19830</v>
       </c>
       <c r="P5" t="n">
-        <v>2760</v>
+        <v>930</v>
       </c>
       <c r="Q5" t="n">
-        <v>17703.35</v>
+        <v>173562.3</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>64440</v>
       </c>
       <c r="H6" t="n">
-        <v>12930</v>
+        <v>13770</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>48</v>
       </c>
       <c r="L6" t="n">
-        <v>161250</v>
+        <v>152250</v>
       </c>
       <c r="M6" t="n">
-        <v>8850</v>
+        <v>14820</v>
       </c>
       <c r="N6" t="n">
-        <v>15660</v>
+        <v>18420</v>
       </c>
       <c r="O6" t="n">
-        <v>20040</v>
+        <v>22560</v>
       </c>
       <c r="P6" t="n">
-        <v>2970</v>
+        <v>1080</v>
       </c>
       <c r="Q6" t="n">
-        <v>21218.84</v>
+        <v>208027.8</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>58290</v>
       </c>
       <c r="H7" t="n">
-        <v>12870</v>
+        <v>13290</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>64</v>
       </c>
       <c r="L7" t="n">
-        <v>179310</v>
+        <v>181800</v>
       </c>
       <c r="M7" t="n">
-        <v>4950</v>
+        <v>13140</v>
       </c>
       <c r="N7" t="n">
-        <v>8010</v>
+        <v>9930</v>
       </c>
       <c r="O7" t="n">
-        <v>19830</v>
+        <v>19320</v>
       </c>
       <c r="P7" t="n">
-        <v>4230</v>
+        <v>1650</v>
       </c>
       <c r="Q7" t="n">
-        <v>22740.79</v>
+        <v>222948.9</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>80190</v>
       </c>
       <c r="H8" t="n">
-        <v>19890</v>
+        <v>18630</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>50</v>
       </c>
       <c r="L8" t="n">
-        <v>218640</v>
+        <v>210270</v>
       </c>
       <c r="M8" t="n">
-        <v>4920</v>
+        <v>12750</v>
       </c>
       <c r="N8" t="n">
-        <v>2400</v>
+        <v>3330</v>
       </c>
       <c r="O8" t="n">
-        <v>21960</v>
+        <v>23190</v>
       </c>
       <c r="P8" t="n">
-        <v>5400</v>
+        <v>3150</v>
       </c>
       <c r="Q8" t="n">
-        <v>23129.56</v>
+        <v>226760.4</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>92250</v>
       </c>
       <c r="H9" t="n">
-        <v>7080</v>
+        <v>8760</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -24093,22 +24093,22 @@
         <v>60</v>
       </c>
       <c r="L9" t="n">
-        <v>246060</v>
+        <v>254640</v>
       </c>
       <c r="M9" t="n">
-        <v>4650</v>
+        <v>11460</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>20460</v>
+        <v>22200</v>
       </c>
       <c r="P9" t="n">
-        <v>8700</v>
+        <v>6240</v>
       </c>
       <c r="Q9" t="n">
-        <v>27465.83</v>
+        <v>269272.8</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>104640</v>
       </c>
       <c r="H10" t="n">
-        <v>840</v>
+        <v>1440</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>57</v>
       </c>
       <c r="L10" t="n">
-        <v>219570</v>
+        <v>232350</v>
       </c>
       <c r="M10" t="n">
-        <v>5130</v>
+        <v>8790</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21330</v>
+        <v>24390</v>
       </c>
       <c r="P10" t="n">
-        <v>11580</v>
+        <v>6660</v>
       </c>
       <c r="Q10" t="n">
-        <v>30234.97</v>
+        <v>296421.3</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>62760</v>
       </c>
       <c r="H11" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>37</v>
       </c>
       <c r="L11" t="n">
-        <v>137010</v>
+        <v>159150</v>
       </c>
       <c r="M11" t="n">
-        <v>3780</v>
+        <v>8040</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12510</v>
+        <v>20160</v>
       </c>
       <c r="P11" t="n">
-        <v>15090</v>
+        <v>7470</v>
       </c>
       <c r="Q11" t="n">
-        <v>26465.94</v>
+        <v>259470</v>
       </c>
     </row>
     <row r="12">
@@ -24240,7 +24240,7 @@
         <v>32520</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -24252,22 +24252,22 @@
         <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>62820</v>
+        <v>77760</v>
       </c>
       <c r="M12" t="n">
-        <v>2520</v>
+        <v>5190</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5850</v>
+        <v>14940</v>
       </c>
       <c r="P12" t="n">
-        <v>15330</v>
+        <v>15360</v>
       </c>
       <c r="Q12" t="n">
-        <v>17017.33</v>
+        <v>166836.6</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>31800</v>
+        <v>41430</v>
       </c>
       <c r="M13" t="n">
-        <v>2130</v>
+        <v>4560</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>3990</v>
       </c>
       <c r="P13" t="n">
-        <v>12420</v>
+        <v>13170</v>
       </c>
       <c r="Q13" t="n">
-        <v>9569.32</v>
+        <v>93816.89999999999</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8760</v>
+        <v>14940</v>
       </c>
       <c r="M14" t="n">
-        <v>1110</v>
+        <v>5220</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1800</v>
+        <v>2040</v>
       </c>
       <c r="P14" t="n">
-        <v>12660</v>
+        <v>11910</v>
       </c>
       <c r="Q14" t="n">
-        <v>4166.43</v>
+        <v>40847.4</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4830</v>
+        <v>9450</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>1770</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2940</v>
       </c>
       <c r="P15" t="n">
-        <v>15570</v>
+        <v>15900</v>
       </c>
       <c r="Q15" t="n">
-        <v>1285.29</v>
+        <v>12600.9</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1050</v>
+        <v>7380</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>840</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="P16" t="n">
-        <v>25860</v>
+        <v>29580</v>
       </c>
       <c r="Q16" t="n">
-        <v>555.48</v>
+        <v>5445.9</v>
       </c>
     </row>
     <row r="17">
@@ -24517,10 +24517,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>360</v>
+        <v>2640</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -24529,10 +24529,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13770</v>
+        <v>18060</v>
       </c>
       <c r="Q17" t="n">
-        <v>222.62</v>
+        <v>2182.5</v>
       </c>
     </row>
     <row r="18">
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>1560</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>16410</v>
+        <v>17700</v>
       </c>
       <c r="Q18" t="n">
-        <v>123.65</v>
+        <v>1212.3</v>
       </c>
     </row>
     <row r="19">
@@ -24623,22 +24623,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>240</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>17880</v>
+        <v>26070</v>
       </c>
       <c r="Q19" t="n">
-        <v>100.06</v>
+        <v>981</v>
       </c>
     </row>
     <row r="20">
@@ -24676,10 +24676,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6420</v>
+        <v>16350</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.79</v>
+        <v>429.3</v>
       </c>
     </row>
     <row r="21">
@@ -24741,10 +24741,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.37</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2376</v>
+        <v>1933.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -25173,22 +25173,22 @@
         <v>22.18</v>
       </c>
       <c r="L5" t="n">
-        <v>34272</v>
+        <v>31140.9</v>
       </c>
       <c r="M5" t="n">
-        <v>398.4</v>
+        <v>622.2</v>
       </c>
       <c r="N5" t="n">
-        <v>208.5</v>
+        <v>202.8</v>
       </c>
       <c r="O5" t="n">
-        <v>982.5</v>
+        <v>991.5</v>
       </c>
       <c r="P5" t="n">
-        <v>55.2</v>
+        <v>18.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>885.17</v>
+        <v>8678.120000000001</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3222</v>
       </c>
       <c r="H6" t="n">
-        <v>7370.1</v>
+        <v>7848.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>24.34</v>
       </c>
       <c r="L6" t="n">
-        <v>59662.5</v>
+        <v>56332.5</v>
       </c>
       <c r="M6" t="n">
-        <v>708</v>
+        <v>1185.6</v>
       </c>
       <c r="N6" t="n">
-        <v>783</v>
+        <v>921</v>
       </c>
       <c r="O6" t="n">
-        <v>5010</v>
+        <v>5640</v>
       </c>
       <c r="P6" t="n">
-        <v>445.5</v>
+        <v>162</v>
       </c>
       <c r="Q6" t="n">
-        <v>15914.13</v>
+        <v>156020.85</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>8743.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9395.1</v>
+        <v>9701.700000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>40.83</v>
       </c>
       <c r="L7" t="n">
-        <v>107586</v>
+        <v>109080</v>
       </c>
       <c r="M7" t="n">
-        <v>1732.5</v>
+        <v>4599</v>
       </c>
       <c r="N7" t="n">
-        <v>560.7</v>
+        <v>695.1</v>
       </c>
       <c r="O7" t="n">
-        <v>6940.5</v>
+        <v>6762</v>
       </c>
       <c r="P7" t="n">
-        <v>1057.5</v>
+        <v>412.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>18192.63</v>
+        <v>178359.12</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>52123.5</v>
       </c>
       <c r="H8" t="n">
-        <v>16906.5</v>
+        <v>15835.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>36.8</v>
       </c>
       <c r="L8" t="n">
-        <v>155234.4</v>
+        <v>149291.7</v>
       </c>
       <c r="M8" t="n">
-        <v>2706</v>
+        <v>7012.5</v>
       </c>
       <c r="N8" t="n">
-        <v>480</v>
+        <v>666</v>
       </c>
       <c r="O8" t="n">
-        <v>9882</v>
+        <v>10435.5</v>
       </c>
       <c r="P8" t="n">
-        <v>2052</v>
+        <v>1197</v>
       </c>
       <c r="Q8" t="n">
-        <v>21973.08</v>
+        <v>215422.38</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>78412.5</v>
       </c>
       <c r="H9" t="n">
-        <v>7080</v>
+        <v>8760</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -25385,22 +25385,22 @@
         <v>48.18</v>
       </c>
       <c r="L9" t="n">
-        <v>199308.6</v>
+        <v>206258.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3255</v>
+        <v>8022</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11253</v>
+        <v>12210</v>
       </c>
       <c r="P9" t="n">
-        <v>4350</v>
+        <v>3120</v>
       </c>
       <c r="Q9" t="n">
-        <v>26641.85</v>
+        <v>261194.62</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>104640</v>
       </c>
       <c r="H10" t="n">
-        <v>840</v>
+        <v>1440</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>49.59</v>
       </c>
       <c r="L10" t="n">
-        <v>195417.3</v>
+        <v>206791.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4360.5</v>
+        <v>7471.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14931</v>
+        <v>17073</v>
       </c>
       <c r="P10" t="n">
-        <v>9843</v>
+        <v>5661</v>
       </c>
       <c r="Q10" t="n">
-        <v>30234.97</v>
+        <v>296421.3</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>62760</v>
       </c>
       <c r="H11" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>33.24</v>
       </c>
       <c r="L11" t="n">
-        <v>137010</v>
+        <v>159150</v>
       </c>
       <c r="M11" t="n">
-        <v>3402</v>
+        <v>7236</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10633.5</v>
+        <v>17136</v>
       </c>
       <c r="P11" t="n">
-        <v>13581</v>
+        <v>6723</v>
       </c>
       <c r="Q11" t="n">
-        <v>26465.94</v>
+        <v>259470</v>
       </c>
     </row>
     <row r="12">
@@ -25532,7 +25532,7 @@
         <v>32520</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -25544,22 +25544,22 @@
         <v>8.34</v>
       </c>
       <c r="L12" t="n">
-        <v>62820</v>
+        <v>77760</v>
       </c>
       <c r="M12" t="n">
-        <v>2394</v>
+        <v>4930.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>5850</v>
+        <v>14940</v>
       </c>
       <c r="P12" t="n">
-        <v>15330</v>
+        <v>15360</v>
       </c>
       <c r="Q12" t="n">
-        <v>17017.33</v>
+        <v>166836.6</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0.95</v>
       </c>
       <c r="L13" t="n">
-        <v>31800</v>
+        <v>41430</v>
       </c>
       <c r="M13" t="n">
-        <v>2130</v>
+        <v>4560</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2460</v>
+        <v>3990</v>
       </c>
       <c r="P13" t="n">
-        <v>12420</v>
+        <v>13170</v>
       </c>
       <c r="Q13" t="n">
-        <v>9569.32</v>
+        <v>93816.89999999999</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>8760</v>
+        <v>14940</v>
       </c>
       <c r="M14" t="n">
-        <v>1110</v>
+        <v>5220</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1800</v>
+        <v>2040</v>
       </c>
       <c r="P14" t="n">
-        <v>12660</v>
+        <v>11910</v>
       </c>
       <c r="Q14" t="n">
-        <v>4166.43</v>
+        <v>40847.4</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4830</v>
+        <v>9450</v>
       </c>
       <c r="M15" t="n">
-        <v>150</v>
+        <v>1770</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2700</v>
+        <v>2940</v>
       </c>
       <c r="P15" t="n">
-        <v>15570</v>
+        <v>15900</v>
       </c>
       <c r="Q15" t="n">
-        <v>1285.29</v>
+        <v>12600.9</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1050</v>
+        <v>7380</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>840</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="P16" t="n">
-        <v>25860</v>
+        <v>29580</v>
       </c>
       <c r="Q16" t="n">
-        <v>555.48</v>
+        <v>5445.9</v>
       </c>
     </row>
     <row r="17">
@@ -25809,10 +25809,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>360</v>
+        <v>2640</v>
       </c>
       <c r="M17" t="n">
-        <v>120</v>
+        <v>750</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -25821,10 +25821,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>13770</v>
+        <v>18060</v>
       </c>
       <c r="Q17" t="n">
-        <v>222.62</v>
+        <v>2182.5</v>
       </c>
     </row>
     <row r="18">
@@ -25862,10 +25862,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>90</v>
+        <v>1560</v>
       </c>
       <c r="M18" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>16410</v>
+        <v>17700</v>
       </c>
       <c r="Q18" t="n">
-        <v>123.65</v>
+        <v>1212.3</v>
       </c>
     </row>
     <row r="19">
@@ -25915,22 +25915,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>240</v>
+        <v>1590</v>
       </c>
       <c r="M19" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>17880</v>
+        <v>26070</v>
       </c>
       <c r="Q19" t="n">
-        <v>100.06</v>
+        <v>981</v>
       </c>
     </row>
     <row r="20">
@@ -25968,10 +25968,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6420</v>
+        <v>16350</v>
       </c>
       <c r="Q20" t="n">
-        <v>43.79</v>
+        <v>429.3</v>
       </c>
     </row>
     <row r="21">
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.37</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>13543200</v>
+        <v>11019240</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -26465,22 +26465,22 @@
         <v>1076826.41</v>
       </c>
       <c r="L5" t="n">
-        <v>6168960</v>
+        <v>5605362</v>
       </c>
       <c r="M5" t="n">
-        <v>139440</v>
+        <v>217770</v>
       </c>
       <c r="N5" t="n">
-        <v>35445</v>
+        <v>34476</v>
       </c>
       <c r="O5" t="n">
-        <v>167025</v>
+        <v>168555</v>
       </c>
       <c r="P5" t="n">
-        <v>3588</v>
+        <v>1209</v>
       </c>
       <c r="Q5" t="n">
-        <v>531100.64</v>
+        <v>5206869</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>173988</v>
       </c>
       <c r="H6" t="n">
-        <v>42009570</v>
+        <v>44738730</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1181658.82</v>
       </c>
       <c r="L6" t="n">
-        <v>10739250</v>
+        <v>10139850</v>
       </c>
       <c r="M6" t="n">
-        <v>247800</v>
+        <v>414960</v>
       </c>
       <c r="N6" t="n">
-        <v>133110</v>
+        <v>156570</v>
       </c>
       <c r="O6" t="n">
-        <v>851700</v>
+        <v>958800</v>
       </c>
       <c r="P6" t="n">
-        <v>28957.5</v>
+        <v>10530</v>
       </c>
       <c r="Q6" t="n">
-        <v>9548476.02</v>
+        <v>93612510</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>472149</v>
       </c>
       <c r="H7" t="n">
-        <v>53552070</v>
+        <v>55299690</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1982638.59</v>
       </c>
       <c r="L7" t="n">
-        <v>19365480</v>
+        <v>19634400</v>
       </c>
       <c r="M7" t="n">
-        <v>606375</v>
+        <v>1609650</v>
       </c>
       <c r="N7" t="n">
-        <v>95319</v>
+        <v>118167</v>
       </c>
       <c r="O7" t="n">
-        <v>1179885</v>
+        <v>1149540</v>
       </c>
       <c r="P7" t="n">
-        <v>68737.5</v>
+        <v>26812.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>10915578.14</v>
+        <v>107015472</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2814669</v>
       </c>
       <c r="H8" t="n">
-        <v>96367050</v>
+        <v>90262350</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>1786860.8</v>
       </c>
       <c r="L8" t="n">
-        <v>27942192</v>
+        <v>26872506</v>
       </c>
       <c r="M8" t="n">
-        <v>947100</v>
+        <v>2454375</v>
       </c>
       <c r="N8" t="n">
-        <v>81600</v>
+        <v>113220</v>
       </c>
       <c r="O8" t="n">
-        <v>1679940</v>
+        <v>1774035</v>
       </c>
       <c r="P8" t="n">
-        <v>133380</v>
+        <v>77805</v>
       </c>
       <c r="Q8" t="n">
-        <v>13183849.66</v>
+        <v>129253428</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4234275</v>
       </c>
       <c r="H9" t="n">
-        <v>40356000</v>
+        <v>49932000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -26677,22 +26677,22 @@
         <v>2339428.08</v>
       </c>
       <c r="L9" t="n">
-        <v>35875548</v>
+        <v>37126512</v>
       </c>
       <c r="M9" t="n">
-        <v>1139250</v>
+        <v>2807700</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1913010</v>
+        <v>2075700</v>
       </c>
       <c r="P9" t="n">
-        <v>282750</v>
+        <v>202800</v>
       </c>
       <c r="Q9" t="n">
-        <v>15985110.5</v>
+        <v>156716769.6</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>5650560</v>
       </c>
       <c r="H10" t="n">
-        <v>4788000</v>
+        <v>8208000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>2407892.04</v>
       </c>
       <c r="L10" t="n">
-        <v>35175114</v>
+        <v>37222470</v>
       </c>
       <c r="M10" t="n">
-        <v>1526175</v>
+        <v>2615025</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2538270</v>
+        <v>2902410</v>
       </c>
       <c r="P10" t="n">
-        <v>639795</v>
+        <v>367965</v>
       </c>
       <c r="Q10" t="n">
-        <v>18140983.56</v>
+        <v>177852780</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>3389040</v>
       </c>
       <c r="H11" t="n">
-        <v>2736000</v>
+        <v>3078000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>1614219.94</v>
       </c>
       <c r="L11" t="n">
-        <v>24661800</v>
+        <v>28647000</v>
       </c>
       <c r="M11" t="n">
-        <v>1190700</v>
+        <v>2532600</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1807695</v>
+        <v>2913120</v>
       </c>
       <c r="P11" t="n">
-        <v>882765</v>
+        <v>436995</v>
       </c>
       <c r="Q11" t="n">
-        <v>15879564</v>
+        <v>155682000</v>
       </c>
     </row>
     <row r="12">
@@ -26824,7 +26824,7 @@
         <v>1756080</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -26836,22 +26836,22 @@
         <v>405102.71</v>
       </c>
       <c r="L12" t="n">
-        <v>11307600</v>
+        <v>13996800</v>
       </c>
       <c r="M12" t="n">
-        <v>837900</v>
+        <v>1725675</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>994500</v>
+        <v>2539800</v>
       </c>
       <c r="P12" t="n">
-        <v>996450</v>
+        <v>998400</v>
       </c>
       <c r="Q12" t="n">
-        <v>10210399.92</v>
+        <v>100101960</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>46103.92</v>
       </c>
       <c r="L13" t="n">
-        <v>5724000</v>
+        <v>7457400</v>
       </c>
       <c r="M13" t="n">
-        <v>745500</v>
+        <v>1596000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>418200</v>
+        <v>678300</v>
       </c>
       <c r="P13" t="n">
-        <v>807300</v>
+        <v>856050</v>
       </c>
       <c r="Q13" t="n">
-        <v>5741594.28</v>
+        <v>56290140</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1576800</v>
+        <v>2689200</v>
       </c>
       <c r="M14" t="n">
-        <v>388500</v>
+        <v>1827000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>306000</v>
+        <v>346800</v>
       </c>
       <c r="P14" t="n">
-        <v>822900</v>
+        <v>774150</v>
       </c>
       <c r="Q14" t="n">
-        <v>2499860.88</v>
+        <v>24508440</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>869400</v>
+        <v>1701000</v>
       </c>
       <c r="M15" t="n">
-        <v>52500</v>
+        <v>619500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>459000</v>
+        <v>499800</v>
       </c>
       <c r="P15" t="n">
-        <v>1012050</v>
+        <v>1033500</v>
       </c>
       <c r="Q15" t="n">
-        <v>771175.08</v>
+        <v>7560540</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>189000</v>
+        <v>1328400</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>294000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>15300</v>
+        <v>81600</v>
       </c>
       <c r="P16" t="n">
-        <v>1680900</v>
+        <v>1922700</v>
       </c>
       <c r="Q16" t="n">
-        <v>333289.08</v>
+        <v>3267540</v>
       </c>
     </row>
     <row r="17">
@@ -27101,10 +27101,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>64800</v>
+        <v>475200</v>
       </c>
       <c r="M17" t="n">
-        <v>42000</v>
+        <v>262500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -27113,10 +27113,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>895050</v>
+        <v>1173900</v>
       </c>
       <c r="Q17" t="n">
-        <v>133569</v>
+        <v>1309500</v>
       </c>
     </row>
     <row r="18">
@@ -27154,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>16200</v>
+        <v>280800</v>
       </c>
       <c r="M18" t="n">
-        <v>10500</v>
+        <v>105000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1066650</v>
+        <v>1150500</v>
       </c>
       <c r="Q18" t="n">
-        <v>74192.75999999999</v>
+        <v>727380</v>
       </c>
     </row>
     <row r="19">
@@ -27207,22 +27207,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>43200</v>
+        <v>286200</v>
       </c>
       <c r="M19" t="n">
-        <v>42000</v>
+        <v>31500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P19" t="n">
-        <v>1162200</v>
+        <v>1694550</v>
       </c>
       <c r="Q19" t="n">
-        <v>60037.2</v>
+        <v>588600</v>
       </c>
     </row>
     <row r="20">
@@ -27260,10 +27260,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>417300</v>
+        <v>1062750</v>
       </c>
       <c r="Q20" t="n">
-        <v>26273.16</v>
+        <v>257580</v>
       </c>
     </row>
     <row r="21">
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q21" t="n">
-        <v>4957.2</v>
+        <v>48600</v>
       </c>
     </row>
     <row r="22">
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>220.32</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="23">
@@ -27692,7 +27692,7 @@
         <v>130290</v>
       </c>
       <c r="H4" t="n">
-        <v>16170</v>
+        <v>17910</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>107</v>
       </c>
       <c r="L4" t="n">
-        <v>405750</v>
+        <v>425220</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>57090</v>
+        <v>54330</v>
       </c>
       <c r="P4" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>43490.23</v>
+        <v>605560.23</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>118260</v>
       </c>
       <c r="H5" t="n">
-        <v>22860</v>
+        <v>23130</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>284310</v>
+        <v>308310</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>56670</v>
+        <v>58620</v>
       </c>
       <c r="P5" t="n">
-        <v>570</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>29819.98</v>
+        <v>415214.91</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>58920</v>
       </c>
       <c r="H6" t="n">
-        <v>15750</v>
+        <v>15210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>36</v>
       </c>
       <c r="L6" t="n">
-        <v>142830</v>
+        <v>148560</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34200</v>
+        <v>35010</v>
       </c>
       <c r="P6" t="n">
-        <v>1530</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>16458.16</v>
+        <v>229164.21</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>39330</v>
       </c>
       <c r="H7" t="n">
-        <v>17430</v>
+        <v>18240</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>17</v>
       </c>
       <c r="L7" t="n">
-        <v>94830</v>
+        <v>98970</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>28740</v>
+        <v>31740</v>
       </c>
       <c r="P7" t="n">
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7290.38</v>
+        <v>101511.63</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>15510</v>
       </c>
       <c r="H8" t="n">
-        <v>2640</v>
+        <v>3120</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>36750</v>
+        <v>41910</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11520</v>
+        <v>13260</v>
       </c>
       <c r="P8" t="n">
-        <v>3870</v>
+        <v>480</v>
       </c>
       <c r="Q8" t="n">
-        <v>3576.76</v>
+        <v>49802.94</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>480</v>
       </c>
       <c r="H9" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5850</v>
+        <v>7560</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5580</v>
+        <v>9750</v>
       </c>
       <c r="P9" t="n">
-        <v>4320</v>
+        <v>1290</v>
       </c>
       <c r="Q9" t="n">
-        <v>183.51</v>
+        <v>2555.19</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>150</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1020</v>
+        <v>1830</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2040</v>
+        <v>7200</v>
       </c>
       <c r="P10" t="n">
-        <v>5550</v>
+        <v>5070</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.71</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>390</v>
+        <v>2550</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>240</v>
+        <v>2490</v>
       </c>
       <c r="P11" t="n">
-        <v>5040</v>
+        <v>8940</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.43</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28137,13 +28137,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>2550</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="13">
@@ -28169,7 +28169,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1410</v>
+        <v>4920</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15">
@@ -28287,7 +28287,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -28299,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8229.6</v>
+        <v>8326.799999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -29049,7 +29049,7 @@
         <v>17.87</v>
       </c>
       <c r="L5" t="n">
-        <v>59705.1</v>
+        <v>64745.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2833.5</v>
+        <v>2931</v>
       </c>
       <c r="P5" t="n">
-        <v>11.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1491</v>
+        <v>20760.75</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2946</v>
       </c>
       <c r="H6" t="n">
-        <v>8977.5</v>
+        <v>8669.700000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>18.25</v>
       </c>
       <c r="L6" t="n">
-        <v>52847.1</v>
+        <v>54967.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8550</v>
+        <v>8752.5</v>
       </c>
       <c r="P6" t="n">
-        <v>229.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12343.62</v>
+        <v>171873.16</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>5899.5</v>
       </c>
       <c r="H7" t="n">
-        <v>12723.9</v>
+        <v>13315.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>10.85</v>
       </c>
       <c r="L7" t="n">
-        <v>56898</v>
+        <v>59382</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10059</v>
+        <v>11109</v>
       </c>
       <c r="P7" t="n">
-        <v>577.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5832.3</v>
+        <v>81209.3</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>10081.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2244</v>
+        <v>2652</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>26092.5</v>
+        <v>29756.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5184</v>
+        <v>5967</v>
       </c>
       <c r="P8" t="n">
-        <v>1470.6</v>
+        <v>182.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3397.92</v>
+        <v>47312.79</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>408</v>
       </c>
       <c r="H9" t="n">
-        <v>420</v>
+        <v>540</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4738.5</v>
+        <v>6123.6</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3069</v>
+        <v>5362.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2160</v>
+        <v>645</v>
       </c>
       <c r="Q9" t="n">
-        <v>178</v>
+        <v>2478.53</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>150</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>907.8</v>
+        <v>1628.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1428</v>
+        <v>5040</v>
       </c>
       <c r="P10" t="n">
-        <v>4717.5</v>
+        <v>4309.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.71</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>390</v>
+        <v>2550</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>204</v>
+        <v>2116.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4536</v>
+        <v>8046</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.43</v>
+        <v>214.83</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29429,13 +29429,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>2550</v>
+        <v>6240</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="13">
@@ -29461,7 +29461,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1410</v>
+        <v>4920</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,10 +29538,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15">
@@ -29579,7 +29579,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -29591,7 +29591,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46908720</v>
+        <v>47462760</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -30341,7 +30341,7 @@
         <v>867889.9399999999</v>
       </c>
       <c r="L5" t="n">
-        <v>10746918</v>
+        <v>11654118</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>481695</v>
+        <v>498270</v>
       </c>
       <c r="P5" t="n">
-        <v>741</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>894599.4</v>
+        <v>12456447.3</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>159084</v>
       </c>
       <c r="H6" t="n">
-        <v>51171750</v>
+        <v>49417290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>886244.11</v>
       </c>
       <c r="L6" t="n">
-        <v>9512478</v>
+        <v>9894096</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1453500</v>
+        <v>1487925</v>
       </c>
       <c r="P6" t="n">
-        <v>14917.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7406170.6</v>
+        <v>103123894.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>318573</v>
       </c>
       <c r="H7" t="n">
-        <v>72526230</v>
+        <v>75896640</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>526638.38</v>
       </c>
       <c r="L7" t="n">
-        <v>10241640</v>
+        <v>10688760</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1710030</v>
+        <v>1888530</v>
       </c>
       <c r="P7" t="n">
-        <v>37537.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3499382.74</v>
+        <v>48725582.4</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>544401</v>
       </c>
       <c r="H8" t="n">
-        <v>12790800</v>
+        <v>15116400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>4696650</v>
+        <v>5356098</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>881280</v>
+        <v>1014390</v>
       </c>
       <c r="P8" t="n">
-        <v>95589</v>
+        <v>11856</v>
       </c>
       <c r="Q8" t="n">
-        <v>2038751.26</v>
+        <v>28387675.8</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>22032</v>
       </c>
       <c r="H9" t="n">
-        <v>2394000</v>
+        <v>3078000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>852930</v>
+        <v>1102248</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>521730</v>
+        <v>911625</v>
       </c>
       <c r="P9" t="n">
-        <v>140400</v>
+        <v>41925</v>
       </c>
       <c r="Q9" t="n">
-        <v>106802.3</v>
+        <v>1487120.58</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>8100</v>
       </c>
       <c r="H10" t="n">
-        <v>342000</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>163404</v>
+        <v>293166</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>242760</v>
+        <v>856800</v>
       </c>
       <c r="P10" t="n">
-        <v>306637.5</v>
+        <v>280117.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>19623.6</v>
+        <v>273240</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>70200</v>
+        <v>459000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>34680</v>
+        <v>359805</v>
       </c>
       <c r="P11" t="n">
-        <v>294840</v>
+        <v>522990</v>
       </c>
       <c r="Q11" t="n">
-        <v>9257.219999999999</v>
+        <v>128898</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>1710000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16200</v>
+        <v>291600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30721,13 +30721,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="P12" t="n">
-        <v>165750</v>
+        <v>405600</v>
       </c>
       <c r="Q12" t="n">
-        <v>2218.32</v>
+        <v>30888</v>
       </c>
     </row>
     <row r="13">
@@ -30753,7 +30753,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>91650</v>
+        <v>319800</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.64</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>11700</v>
+        <v>66300</v>
       </c>
       <c r="Q14" t="n">
-        <v>85.31999999999999</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15">
@@ -30871,7 +30871,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -30883,7 +30883,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
